--- a/research/traditional_assets/database/data/ghana/ghana_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_drugs_pharmaceutical.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1903621821470889</v>
+        <v>0.1899200266917212</v>
       </c>
       <c r="C2">
-        <v>1.805738770945706</v>
+        <v>1.794508270718303</v>
       </c>
       <c r="D2">
-        <v>1.769738770945706</v>
+        <v>1.775168270718303</v>
       </c>
       <c r="E2">
-        <v>-0.73</v>
+        <v>-0.71334</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.01666</v>
       </c>
       <c r="G2">
         <v>0.036</v>
@@ -1433,28 +1433,28 @@
         <v>0.217</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0008379980000000001</v>
       </c>
       <c r="N2">
-        <v>0.217</v>
+        <v>0.216162002</v>
       </c>
       <c r="O2">
-        <v>0.05424999999999999</v>
+        <v>0.05404050049999999</v>
       </c>
       <c r="P2">
-        <v>0.16275</v>
+        <v>0.1621215015</v>
       </c>
       <c r="Q2">
-        <v>0.21575</v>
+        <v>0.2151215015</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1903621821470889</v>
+        <v>0.1914573501936578</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286289</v>
+        <v>0.8908222216697549</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>258.950498688541</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1899200266917212</v>
+        <v>0.1894778712363535</v>
       </c>
       <c r="C3">
-        <v>1.794508270718303</v>
+        <v>1.783311188064862</v>
       </c>
       <c r="D3">
-        <v>1.775168270718303</v>
+        <v>1.780631188064862</v>
       </c>
       <c r="E3">
-        <v>-0.71334</v>
+        <v>-0.69668</v>
       </c>
       <c r="F3">
-        <v>0.01666</v>
+        <v>0.03332</v>
       </c>
       <c r="G3">
         <v>0.036</v>
@@ -1515,28 +1515,28 @@
         <v>0.217</v>
       </c>
       <c r="M3">
-        <v>0.0008379980000000001</v>
+        <v>0.001675996</v>
       </c>
       <c r="N3">
-        <v>0.216162002</v>
+        <v>0.215324004</v>
       </c>
       <c r="O3">
-        <v>0.05404050049999999</v>
+        <v>0.05383100099999999</v>
       </c>
       <c r="P3">
-        <v>0.1621215015</v>
+        <v>0.161493003</v>
       </c>
       <c r="Q3">
-        <v>0.2151215015</v>
+        <v>0.214493003</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1914573501936578</v>
+        <v>0.192574868608524</v>
       </c>
       <c r="T3">
-        <v>0.8908222216697549</v>
+        <v>0.897656825181108</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>258.950498688541</v>
+        <v>129.4752493442705</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1894778712363535</v>
+        <v>0.1890357157809857</v>
       </c>
       <c r="C4">
-        <v>1.783311188064862</v>
+        <v>1.772147832456298</v>
       </c>
       <c r="D4">
-        <v>1.780631188064862</v>
+        <v>1.786127832456298</v>
       </c>
       <c r="E4">
-        <v>-0.69668</v>
+        <v>-0.68002</v>
       </c>
       <c r="F4">
-        <v>0.03332</v>
+        <v>0.04998</v>
       </c>
       <c r="G4">
         <v>0.036</v>
@@ -1597,28 +1597,28 @@
         <v>0.217</v>
       </c>
       <c r="M4">
-        <v>0.001675996</v>
+        <v>0.002513994</v>
       </c>
       <c r="N4">
-        <v>0.215324004</v>
+        <v>0.214486006</v>
       </c>
       <c r="O4">
-        <v>0.05383100099999999</v>
+        <v>0.05362150149999999</v>
       </c>
       <c r="P4">
-        <v>0.161493003</v>
+        <v>0.1608645045</v>
       </c>
       <c r="Q4">
-        <v>0.214493003</v>
+        <v>0.2138645045</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.192574868608524</v>
+        <v>0.1937154286401915</v>
       </c>
       <c r="T4">
-        <v>0.897656825181108</v>
+        <v>0.9046323483524888</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>129.4752493442705</v>
+        <v>86.31683289618034</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1890357157809857</v>
+        <v>0.1885935603256181</v>
       </c>
       <c r="C5">
-        <v>1.772147832456298</v>
+        <v>1.761018517196588</v>
       </c>
       <c r="D5">
-        <v>1.786127832456298</v>
+        <v>1.791658517196588</v>
       </c>
       <c r="E5">
-        <v>-0.68002</v>
+        <v>-0.6633599999999999</v>
       </c>
       <c r="F5">
-        <v>0.04998</v>
+        <v>0.06664</v>
       </c>
       <c r="G5">
         <v>0.036</v>
@@ -1679,28 +1679,28 @@
         <v>0.217</v>
       </c>
       <c r="M5">
-        <v>0.002513994</v>
+        <v>0.003351992</v>
       </c>
       <c r="N5">
-        <v>0.214486006</v>
+        <v>0.213648008</v>
       </c>
       <c r="O5">
-        <v>0.05362150149999999</v>
+        <v>0.05341200199999999</v>
       </c>
       <c r="P5">
-        <v>0.1608645045</v>
+        <v>0.160236006</v>
       </c>
       <c r="Q5">
-        <v>0.2138645045</v>
+        <v>0.213236006</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1937154286401915</v>
+        <v>0.1948797503391855</v>
       </c>
       <c r="T5">
-        <v>0.9046323483524888</v>
+        <v>0.9117531949232736</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>86.31683289618034</v>
+        <v>64.73762467213524</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1885935603256181</v>
+        <v>0.1881514048702503</v>
       </c>
       <c r="C6">
-        <v>1.761018517196588</v>
+        <v>1.749923559482308</v>
       </c>
       <c r="D6">
-        <v>1.791658517196588</v>
+        <v>1.797223559482308</v>
       </c>
       <c r="E6">
-        <v>-0.6633599999999999</v>
+        <v>-0.6466999999999999</v>
       </c>
       <c r="F6">
-        <v>0.06664</v>
+        <v>0.0833</v>
       </c>
       <c r="G6">
         <v>0.036</v>
@@ -1761,28 +1761,28 @@
         <v>0.217</v>
       </c>
       <c r="M6">
-        <v>0.003351992</v>
+        <v>0.004189989999999999</v>
       </c>
       <c r="N6">
-        <v>0.213648008</v>
+        <v>0.21281001</v>
       </c>
       <c r="O6">
-        <v>0.05341200199999999</v>
+        <v>0.05320250249999999</v>
       </c>
       <c r="P6">
-        <v>0.160236006</v>
+        <v>0.1596075075</v>
       </c>
       <c r="Q6">
-        <v>0.213236006</v>
+        <v>0.2126075075</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1948797503391855</v>
+        <v>0.1960685840739477</v>
       </c>
       <c r="T6">
-        <v>0.9117531949232736</v>
+        <v>0.9190239540534433</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>64.73762467213524</v>
+        <v>51.7900997377082</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1881514048702503</v>
+        <v>0.1877092494148826</v>
       </c>
       <c r="C7">
-        <v>1.749923559482308</v>
+        <v>1.738863280463266</v>
       </c>
       <c r="D7">
-        <v>1.797223559482308</v>
+        <v>1.802823280463266</v>
       </c>
       <c r="E7">
-        <v>-0.6466999999999999</v>
+        <v>-0.6300399999999999</v>
       </c>
       <c r="F7">
-        <v>0.0833</v>
+        <v>0.09996000000000001</v>
       </c>
       <c r="G7">
         <v>0.036</v>
@@ -1843,28 +1843,28 @@
         <v>0.217</v>
       </c>
       <c r="M7">
-        <v>0.004189989999999999</v>
+        <v>0.005027988</v>
       </c>
       <c r="N7">
-        <v>0.21281001</v>
+        <v>0.211972012</v>
       </c>
       <c r="O7">
-        <v>0.05320250249999999</v>
+        <v>0.05299300299999999</v>
       </c>
       <c r="P7">
-        <v>0.1596075075</v>
+        <v>0.158979009</v>
       </c>
       <c r="Q7">
-        <v>0.2126075075</v>
+        <v>0.211979009</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1960685840739477</v>
+        <v>0.1972827121434921</v>
       </c>
       <c r="T7">
-        <v>0.9190239540534433</v>
+        <v>0.9264494101863824</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>51.7900997377082</v>
+        <v>43.15841644809016</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1877092494148826</v>
+        <v>0.1872670939595149</v>
       </c>
       <c r="C8">
-        <v>1.738863280463266</v>
+        <v>1.727838005304287</v>
       </c>
       <c r="D8">
-        <v>1.802823280463266</v>
+        <v>1.808458005304287</v>
       </c>
       <c r="E8">
-        <v>-0.6300399999999999</v>
+        <v>-0.61338</v>
       </c>
       <c r="F8">
-        <v>0.09995999999999999</v>
+        <v>0.11662</v>
       </c>
       <c r="G8">
         <v>0.036</v>
@@ -1925,28 +1925,28 @@
         <v>0.217</v>
       </c>
       <c r="M8">
-        <v>0.005027988</v>
+        <v>0.005865985999999999</v>
       </c>
       <c r="N8">
-        <v>0.211972012</v>
+        <v>0.211134014</v>
       </c>
       <c r="O8">
-        <v>0.05299300299999999</v>
+        <v>0.0527835035</v>
       </c>
       <c r="P8">
-        <v>0.158979009</v>
+        <v>0.1583505105</v>
       </c>
       <c r="Q8">
-        <v>0.211979009</v>
+        <v>0.2113505105</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1972827121434921</v>
+        <v>0.198522950494102</v>
       </c>
       <c r="T8">
-        <v>0.9264494101863824</v>
+        <v>0.9340345535479869</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>43.15841644809016</v>
+        <v>36.99292838407729</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1872670939595149</v>
+        <v>0.1868249385041472</v>
       </c>
       <c r="C9">
-        <v>1.727838005304287</v>
+        <v>1.716848063248153</v>
       </c>
       <c r="D9">
-        <v>1.808458005304287</v>
+        <v>1.814128063248153</v>
       </c>
       <c r="E9">
-        <v>-0.61338</v>
+        <v>-0.5967199999999999</v>
       </c>
       <c r="F9">
-        <v>0.11662</v>
+        <v>0.13328</v>
       </c>
       <c r="G9">
         <v>0.036</v>
@@ -2007,28 +2007,28 @@
         <v>0.217</v>
       </c>
       <c r="M9">
-        <v>0.005865986</v>
+        <v>0.006703984000000001</v>
       </c>
       <c r="N9">
-        <v>0.211134014</v>
+        <v>0.210296016</v>
       </c>
       <c r="O9">
-        <v>0.0527835035</v>
+        <v>0.05257400399999999</v>
       </c>
       <c r="P9">
-        <v>0.1583505105</v>
+        <v>0.157722012</v>
       </c>
       <c r="Q9">
-        <v>0.2113505105</v>
+        <v>0.210722012</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.198522950494102</v>
+        <v>0.199790150547986</v>
       </c>
       <c r="T9">
-        <v>0.9340345535479869</v>
+        <v>0.9417845913304961</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.99292838407729</v>
+        <v>32.36881233606762</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1868249385041472</v>
+        <v>0.1863827830487794</v>
       </c>
       <c r="C10">
-        <v>1.716848063248153</v>
+        <v>1.705893787679733</v>
       </c>
       <c r="D10">
-        <v>1.814128063248153</v>
+        <v>1.819833787679733</v>
       </c>
       <c r="E10">
-        <v>-0.5967199999999999</v>
+        <v>-0.58006</v>
       </c>
       <c r="F10">
-        <v>0.13328</v>
+        <v>0.14994</v>
       </c>
       <c r="G10">
         <v>0.036</v>
@@ -2089,28 +2089,28 @@
         <v>0.217</v>
       </c>
       <c r="M10">
-        <v>0.006703984000000001</v>
+        <v>0.007541981999999999</v>
       </c>
       <c r="N10">
-        <v>0.210296016</v>
+        <v>0.209458018</v>
       </c>
       <c r="O10">
-        <v>0.05257400399999999</v>
+        <v>0.05236450449999999</v>
       </c>
       <c r="P10">
-        <v>0.157722012</v>
+        <v>0.1570935135</v>
       </c>
       <c r="Q10">
-        <v>0.210722012</v>
+        <v>0.2100935135</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.199790150547986</v>
+        <v>0.2010852011525049</v>
       </c>
       <c r="T10">
-        <v>0.9417845913304961</v>
+        <v>0.9497049596137195</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>32.36881233606762</v>
+        <v>28.77227763206011</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1863827830487794</v>
+        <v>0.1859406275934117</v>
       </c>
       <c r="C11">
-        <v>1.705893787679733</v>
+        <v>1.694975516191322</v>
       </c>
       <c r="D11">
-        <v>1.819833787679733</v>
+        <v>1.825575516191322</v>
       </c>
       <c r="E11">
-        <v>-0.58006</v>
+        <v>-0.5634</v>
       </c>
       <c r="F11">
-        <v>0.14994</v>
+        <v>0.1666</v>
       </c>
       <c r="G11">
         <v>0.036</v>
@@ -2171,28 +2171,28 @@
         <v>0.217</v>
       </c>
       <c r="M11">
-        <v>0.007541981999999999</v>
+        <v>0.008379979999999999</v>
       </c>
       <c r="N11">
-        <v>0.209458018</v>
+        <v>0.20862002</v>
       </c>
       <c r="O11">
-        <v>0.05236450449999999</v>
+        <v>0.05215500499999999</v>
       </c>
       <c r="P11">
-        <v>0.1570935135</v>
+        <v>0.156465015</v>
       </c>
       <c r="Q11">
-        <v>0.2100935135</v>
+        <v>0.209465015</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2010852011525049</v>
+        <v>0.2024090306593463</v>
       </c>
       <c r="T11">
-        <v>0.9497049596137195</v>
+        <v>0.9578013360810146</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.77227763206011</v>
+        <v>25.8950498688541</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1859406275934117</v>
+        <v>0.185498472138044</v>
       </c>
       <c r="C12">
-        <v>1.694975516191322</v>
+        <v>1.684093590649231</v>
       </c>
       <c r="D12">
-        <v>1.825575516191322</v>
+        <v>1.831353590649231</v>
       </c>
       <c r="E12">
-        <v>-0.5634</v>
+        <v>-0.54674</v>
       </c>
       <c r="F12">
-        <v>0.1666</v>
+        <v>0.18326</v>
       </c>
       <c r="G12">
         <v>0.036</v>
@@ -2253,28 +2253,28 @@
         <v>0.217</v>
       </c>
       <c r="M12">
-        <v>0.008379979999999999</v>
+        <v>0.009217978</v>
       </c>
       <c r="N12">
-        <v>0.20862002</v>
+        <v>0.207782022</v>
       </c>
       <c r="O12">
-        <v>0.05215500499999999</v>
+        <v>0.0519455055</v>
       </c>
       <c r="P12">
-        <v>0.156465015</v>
+        <v>0.1558365165</v>
       </c>
       <c r="Q12">
-        <v>0.209465015</v>
+        <v>0.2088365165</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2024090306593463</v>
+        <v>0.2037626091438696</v>
       </c>
       <c r="T12">
-        <v>0.9578013360810146</v>
+        <v>0.9660796535925187</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.8950498688541</v>
+        <v>23.540954426231</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.185498472138044</v>
+        <v>0.1850563166826762</v>
       </c>
       <c r="C13">
-        <v>1.684093590649231</v>
+        <v>1.673248357261636</v>
       </c>
       <c r="D13">
-        <v>1.831353590649231</v>
+        <v>1.837168357261636</v>
       </c>
       <c r="E13">
-        <v>-0.54674</v>
+        <v>-0.53008</v>
       </c>
       <c r="F13">
-        <v>0.18326</v>
+        <v>0.19992</v>
       </c>
       <c r="G13">
         <v>0.036</v>
@@ -2335,28 +2335,28 @@
         <v>0.217</v>
       </c>
       <c r="M13">
-        <v>0.009217978</v>
+        <v>0.010055976</v>
       </c>
       <c r="N13">
-        <v>0.207782022</v>
+        <v>0.206944024</v>
       </c>
       <c r="O13">
-        <v>0.0519455055</v>
+        <v>0.05173600599999999</v>
       </c>
       <c r="P13">
-        <v>0.1558365165</v>
+        <v>0.155208018</v>
       </c>
       <c r="Q13">
-        <v>0.2088365165</v>
+        <v>0.208208018</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2037626091438696</v>
+        <v>0.2051469507757685</v>
       </c>
       <c r="T13">
-        <v>0.9660796535925187</v>
+        <v>0.9745461146838296</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.540954426231</v>
+        <v>21.57920822404508</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1850563166826762</v>
+        <v>0.1846141612273085</v>
       </c>
       <c r="C14">
-        <v>1.673248357261636</v>
+        <v>1.662440166647726</v>
       </c>
       <c r="D14">
-        <v>1.837168357261636</v>
+        <v>1.843020166647726</v>
       </c>
       <c r="E14">
-        <v>-0.53008</v>
+        <v>-0.51342</v>
       </c>
       <c r="F14">
-        <v>0.19992</v>
+        <v>0.21658</v>
       </c>
       <c r="G14">
         <v>0.036</v>
@@ -2417,28 +2417,28 @@
         <v>0.217</v>
       </c>
       <c r="M14">
-        <v>0.010055976</v>
+        <v>0.010893974</v>
       </c>
       <c r="N14">
-        <v>0.206944024</v>
+        <v>0.206106026</v>
       </c>
       <c r="O14">
-        <v>0.05173600599999999</v>
+        <v>0.05152650649999999</v>
       </c>
       <c r="P14">
-        <v>0.155208018</v>
+        <v>0.1545795195</v>
       </c>
       <c r="Q14">
-        <v>0.208208018</v>
+        <v>0.2075795195</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2051469507757685</v>
+        <v>0.2065631163532282</v>
       </c>
       <c r="T14">
-        <v>0.9745461146838296</v>
+        <v>0.9832072070645959</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.57920822404508</v>
+        <v>19.91926912988777</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1846141612273085</v>
+        <v>0.1841720057719408</v>
       </c>
       <c r="C15">
-        <v>1.662440166647726</v>
+        <v>1.651669373908182</v>
       </c>
       <c r="D15">
-        <v>1.843020166647726</v>
+        <v>1.848909373908182</v>
       </c>
       <c r="E15">
-        <v>-0.51342</v>
+        <v>-0.49676</v>
       </c>
       <c r="F15">
-        <v>0.21658</v>
+        <v>0.23324</v>
       </c>
       <c r="G15">
         <v>0.036</v>
@@ -2499,28 +2499,28 @@
         <v>0.217</v>
       </c>
       <c r="M15">
-        <v>0.010893974</v>
+        <v>0.011731972</v>
       </c>
       <c r="N15">
-        <v>0.206106026</v>
+        <v>0.205268028</v>
       </c>
       <c r="O15">
-        <v>0.05152650649999999</v>
+        <v>0.05131700699999999</v>
       </c>
       <c r="P15">
-        <v>0.1545795195</v>
+        <v>0.153951021</v>
       </c>
       <c r="Q15">
-        <v>0.2075795195</v>
+        <v>0.206951021</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2065631163532282</v>
+        <v>0.2080122160138847</v>
       </c>
       <c r="T15">
-        <v>0.9832072070645959</v>
+        <v>0.9920697201984033</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.91926912988777</v>
+        <v>18.49646419203864</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1841720057719408</v>
+        <v>0.1837298503165731</v>
       </c>
       <c r="C16">
-        <v>1.651669373908182</v>
+        <v>1.640936338697006</v>
       </c>
       <c r="D16">
-        <v>1.848909373908182</v>
+        <v>1.854836338697005</v>
       </c>
       <c r="E16">
-        <v>-0.49676</v>
+        <v>-0.4801</v>
       </c>
       <c r="F16">
-        <v>0.23324</v>
+        <v>0.2499</v>
       </c>
       <c r="G16">
         <v>0.036</v>
@@ -2581,28 +2581,28 @@
         <v>0.217</v>
       </c>
       <c r="M16">
-        <v>0.011731972</v>
+        <v>0.01256997</v>
       </c>
       <c r="N16">
-        <v>0.205268028</v>
+        <v>0.20443003</v>
       </c>
       <c r="O16">
-        <v>0.05131700699999999</v>
+        <v>0.05110750749999999</v>
       </c>
       <c r="P16">
-        <v>0.153951021</v>
+        <v>0.1533225225</v>
       </c>
       <c r="Q16">
-        <v>0.206951021</v>
+        <v>0.2063225225</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2080122160138847</v>
+        <v>0.2094954121371448</v>
       </c>
       <c r="T16">
-        <v>0.9920697201984033</v>
+        <v>1.001140763053006</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.49646419203864</v>
+        <v>17.26336657923606</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1837298503165731</v>
+        <v>0.1832876948612054</v>
       </c>
       <c r="C17">
-        <v>1.640936338697006</v>
+        <v>1.630241425294734</v>
       </c>
       <c r="D17">
-        <v>1.854836338697005</v>
+        <v>1.860801425294734</v>
       </c>
       <c r="E17">
-        <v>-0.4801</v>
+        <v>-0.46344</v>
       </c>
       <c r="F17">
-        <v>0.2499</v>
+        <v>0.26656</v>
       </c>
       <c r="G17">
         <v>0.036</v>
@@ -2663,28 +2663,28 @@
         <v>0.217</v>
       </c>
       <c r="M17">
-        <v>0.01256997</v>
+        <v>0.013407968</v>
       </c>
       <c r="N17">
-        <v>0.20443003</v>
+        <v>0.203592032</v>
       </c>
       <c r="O17">
-        <v>0.0511075075</v>
+        <v>0.05089800799999999</v>
       </c>
       <c r="P17">
-        <v>0.1533225225</v>
+        <v>0.152694024</v>
       </c>
       <c r="Q17">
-        <v>0.2063225225</v>
+        <v>0.205694024</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2094954121371448</v>
+        <v>0.2110139224538159</v>
       </c>
       <c r="T17">
-        <v>1.001140763053006</v>
+        <v>1.010427783118433</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.26336657923607</v>
+        <v>16.18440616803381</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1832876948612054</v>
+        <v>0.1828455394058377</v>
       </c>
       <c r="C18">
-        <v>1.630241425294734</v>
+        <v>1.619585002683076</v>
       </c>
       <c r="D18">
-        <v>1.860801425294734</v>
+        <v>1.866805002683076</v>
       </c>
       <c r="E18">
-        <v>-0.46344</v>
+        <v>-0.44678</v>
       </c>
       <c r="F18">
-        <v>0.26656</v>
+        <v>0.28322</v>
       </c>
       <c r="G18">
         <v>0.036</v>
@@ -2745,28 +2745,28 @@
         <v>0.217</v>
       </c>
       <c r="M18">
-        <v>0.013407968</v>
+        <v>0.014245966</v>
       </c>
       <c r="N18">
-        <v>0.203592032</v>
+        <v>0.202754034</v>
       </c>
       <c r="O18">
-        <v>0.05089800799999999</v>
+        <v>0.05068850849999999</v>
       </c>
       <c r="P18">
-        <v>0.152694024</v>
+        <v>0.1520655255</v>
       </c>
       <c r="Q18">
-        <v>0.205694024</v>
+        <v>0.2050655255</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2110139224538159</v>
+        <v>0.2125690233805273</v>
       </c>
       <c r="T18">
-        <v>1.010427783118433</v>
+        <v>1.019938586799894</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.18440616803381</v>
+        <v>15.23238227579653</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1828455394058377</v>
+        <v>0.1824033839504699</v>
       </c>
       <c r="C19">
-        <v>1.619585002683076</v>
+        <v>1.608967444620996</v>
       </c>
       <c r="D19">
-        <v>1.866805002683076</v>
+        <v>1.872847444620996</v>
       </c>
       <c r="E19">
-        <v>-0.44678</v>
+        <v>-0.4301199999999999</v>
       </c>
       <c r="F19">
-        <v>0.28322</v>
+        <v>0.29988</v>
       </c>
       <c r="G19">
         <v>0.036</v>
@@ -2827,28 +2827,28 @@
         <v>0.217</v>
       </c>
       <c r="M19">
-        <v>0.014245966</v>
+        <v>0.015083964</v>
       </c>
       <c r="N19">
-        <v>0.202754034</v>
+        <v>0.201916036</v>
       </c>
       <c r="O19">
-        <v>0.05068850849999999</v>
+        <v>0.05047900899999999</v>
       </c>
       <c r="P19">
-        <v>0.1520655255</v>
+        <v>0.151437027</v>
       </c>
       <c r="Q19">
-        <v>0.2050655255</v>
+        <v>0.204437027</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2125690233805273</v>
+        <v>0.2141620535981341</v>
       </c>
       <c r="T19">
-        <v>1.019938586799894</v>
+        <v>1.029681361302854</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.23238227579653</v>
+        <v>14.38613881603005</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.18240338395047</v>
+        <v>0.1819612284951022</v>
       </c>
       <c r="C20">
-        <v>1.608967444620996</v>
+        <v>1.598389129722276</v>
       </c>
       <c r="D20">
-        <v>1.872847444620996</v>
+        <v>1.878929129722276</v>
       </c>
       <c r="E20">
-        <v>-0.43012</v>
+        <v>-0.41346</v>
       </c>
       <c r="F20">
-        <v>0.29988</v>
+        <v>0.31654</v>
       </c>
       <c r="G20">
         <v>0.036</v>
@@ -2909,28 +2909,28 @@
         <v>0.217</v>
       </c>
       <c r="M20">
-        <v>0.015083964</v>
+        <v>0.015921962</v>
       </c>
       <c r="N20">
-        <v>0.201916036</v>
+        <v>0.201078038</v>
       </c>
       <c r="O20">
-        <v>0.05047900899999999</v>
+        <v>0.05026950949999999</v>
       </c>
       <c r="P20">
-        <v>0.151437027</v>
+        <v>0.1508085285</v>
       </c>
       <c r="Q20">
-        <v>0.204437027</v>
+        <v>0.2038085285</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2141620535981341</v>
+        <v>0.2157944178951879</v>
       </c>
       <c r="T20">
-        <v>1.029681361302854</v>
+        <v>1.039664698139221</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.38613881603006</v>
+        <v>13.62897361518637</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1819612284951022</v>
+        <v>0.1815190730397345</v>
       </c>
       <c r="C21">
-        <v>1.598389129722276</v>
+        <v>1.587850441534602</v>
       </c>
       <c r="D21">
-        <v>1.878929129722276</v>
+        <v>1.885050441534602</v>
       </c>
       <c r="E21">
-        <v>-0.41346</v>
+        <v>-0.3968</v>
       </c>
       <c r="F21">
-        <v>0.31654</v>
+        <v>0.3332</v>
       </c>
       <c r="G21">
         <v>0.036</v>
@@ -2991,28 +2991,28 @@
         <v>0.217</v>
       </c>
       <c r="M21">
-        <v>0.015921962</v>
+        <v>0.01675996</v>
       </c>
       <c r="N21">
-        <v>0.201078038</v>
+        <v>0.20024004</v>
       </c>
       <c r="O21">
-        <v>0.05026950949999999</v>
+        <v>0.05006001</v>
       </c>
       <c r="P21">
-        <v>0.1508085285</v>
+        <v>0.15018003</v>
       </c>
       <c r="Q21">
-        <v>0.2038085285</v>
+        <v>0.20318003</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2157944178951879</v>
+        <v>0.2174675912996681</v>
       </c>
       <c r="T21">
-        <v>1.039664698139221</v>
+        <v>1.049897618396497</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.62897361518637</v>
+        <v>12.94752493442705</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1815190730397345</v>
+        <v>0.1813131675843668</v>
       </c>
       <c r="C22">
-        <v>1.587850441534602</v>
+        <v>1.574054681050763</v>
       </c>
       <c r="D22">
-        <v>1.885050441534602</v>
+        <v>1.887914681050763</v>
       </c>
       <c r="E22">
-        <v>-0.3968</v>
+        <v>-0.38014</v>
       </c>
       <c r="F22">
-        <v>0.3332</v>
+        <v>0.34986</v>
       </c>
       <c r="G22">
         <v>0.036</v>
@@ -3073,45 +3073,45 @@
         <v>0.217</v>
       </c>
       <c r="M22">
-        <v>0.01675996</v>
+        <v>0.018122748</v>
       </c>
       <c r="N22">
-        <v>0.20024004</v>
+        <v>0.198877252</v>
       </c>
       <c r="O22">
-        <v>0.05006001</v>
+        <v>0.04971931299999999</v>
       </c>
       <c r="P22">
-        <v>0.15018003</v>
+        <v>0.149157939</v>
       </c>
       <c r="Q22">
-        <v>0.20318003</v>
+        <v>0.202157939</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2174675912996681</v>
+        <v>0.2191831235245149</v>
       </c>
       <c r="T22">
-        <v>1.049897618396497</v>
+        <v>1.060389599926109</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>12.94752493442705</v>
+        <v>11.97390152972386</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1813131675843668</v>
+        <v>0.180882262128999</v>
       </c>
       <c r="C23">
-        <v>1.574054681050763</v>
+        <v>1.563417031598586</v>
       </c>
       <c r="D23">
-        <v>1.887914681050763</v>
+        <v>1.893937031598586</v>
       </c>
       <c r="E23">
-        <v>-0.38014</v>
+        <v>-0.36348</v>
       </c>
       <c r="F23">
-        <v>0.3498599999999999</v>
+        <v>0.36652</v>
       </c>
       <c r="G23">
         <v>0.036</v>
@@ -3155,28 +3155,28 @@
         <v>0.217</v>
       </c>
       <c r="M23">
-        <v>0.018122748</v>
+        <v>0.018985736</v>
       </c>
       <c r="N23">
-        <v>0.198877252</v>
+        <v>0.198014264</v>
       </c>
       <c r="O23">
-        <v>0.04971931299999999</v>
+        <v>0.04950356599999999</v>
       </c>
       <c r="P23">
-        <v>0.149157939</v>
+        <v>0.148510698</v>
       </c>
       <c r="Q23">
-        <v>0.202157939</v>
+        <v>0.201510698</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2191831235245149</v>
+        <v>0.220942643755127</v>
       </c>
       <c r="T23">
-        <v>1.060389599926109</v>
+        <v>1.071150606623146</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.97390152972386</v>
+        <v>11.42963327837277</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.180882262128999</v>
+        <v>0.1804513566736313</v>
       </c>
       <c r="C24">
-        <v>1.563417031598586</v>
+        <v>1.552817927078583</v>
       </c>
       <c r="D24">
-        <v>1.893937031598586</v>
+        <v>1.899997927078583</v>
       </c>
       <c r="E24">
-        <v>-0.36348</v>
+        <v>-0.34682</v>
       </c>
       <c r="F24">
-        <v>0.36652</v>
+        <v>0.38318</v>
       </c>
       <c r="G24">
         <v>0.036</v>
@@ -3237,28 +3237,28 @@
         <v>0.217</v>
       </c>
       <c r="M24">
-        <v>0.018985736</v>
+        <v>0.019848724</v>
       </c>
       <c r="N24">
-        <v>0.198014264</v>
+        <v>0.197151276</v>
       </c>
       <c r="O24">
-        <v>0.04950356599999999</v>
+        <v>0.04928781899999999</v>
       </c>
       <c r="P24">
-        <v>0.148510698</v>
+        <v>0.147863457</v>
       </c>
       <c r="Q24">
-        <v>0.201510698</v>
+        <v>0.200863457</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.220942643755127</v>
+        <v>0.2227478658099108</v>
       </c>
       <c r="T24">
-        <v>1.071150606623146</v>
+        <v>1.08219111998764</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.42963327837277</v>
+        <v>10.93269270105222</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1804513566736313</v>
+        <v>0.1800204512182636</v>
       </c>
       <c r="C25">
-        <v>1.552817927078583</v>
+        <v>1.542257738728255</v>
       </c>
       <c r="D25">
-        <v>1.899997927078583</v>
+        <v>1.906097738728255</v>
       </c>
       <c r="E25">
-        <v>-0.34682</v>
+        <v>-0.33016</v>
       </c>
       <c r="F25">
-        <v>0.38318</v>
+        <v>0.39984</v>
       </c>
       <c r="G25">
         <v>0.036</v>
@@ -3319,28 +3319,28 @@
         <v>0.217</v>
       </c>
       <c r="M25">
-        <v>0.019848724</v>
+        <v>0.020711712</v>
       </c>
       <c r="N25">
-        <v>0.197151276</v>
+        <v>0.196288288</v>
       </c>
       <c r="O25">
-        <v>0.04928781899999999</v>
+        <v>0.04907207199999999</v>
       </c>
       <c r="P25">
-        <v>0.147863457</v>
+        <v>0.147216216</v>
       </c>
       <c r="Q25">
-        <v>0.200863457</v>
+        <v>0.200216216</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2227478658099108</v>
+        <v>0.2246005937082416</v>
       </c>
       <c r="T25">
-        <v>1.08219111998764</v>
+        <v>1.093522173177515</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.93269270105222</v>
+        <v>10.47716383850837</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1800204512182636</v>
+        <v>0.1795895457628959</v>
       </c>
       <c r="C26">
-        <v>1.542257738728255</v>
+        <v>1.531736842567787</v>
       </c>
       <c r="D26">
-        <v>1.906097738728255</v>
+        <v>1.912236842567787</v>
       </c>
       <c r="E26">
-        <v>-0.33016</v>
+        <v>-0.3135</v>
       </c>
       <c r="F26">
-        <v>0.39984</v>
+        <v>0.4165</v>
       </c>
       <c r="G26">
         <v>0.036</v>
@@ -3401,28 +3401,28 @@
         <v>0.217</v>
       </c>
       <c r="M26">
-        <v>0.020711712</v>
+        <v>0.0215747</v>
       </c>
       <c r="N26">
-        <v>0.196288288</v>
+        <v>0.1954253</v>
       </c>
       <c r="O26">
-        <v>0.04907207199999999</v>
+        <v>0.04885632499999999</v>
       </c>
       <c r="P26">
-        <v>0.147216216</v>
+        <v>0.146568975</v>
       </c>
       <c r="Q26">
-        <v>0.200216216</v>
+        <v>0.199568975</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2246005937082416</v>
+        <v>0.2265027276838611</v>
       </c>
       <c r="T26">
-        <v>1.093522173177515</v>
+        <v>1.105155387785786</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.47716383850838</v>
+        <v>10.05807728496804</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1795895457628959</v>
+        <v>0.1794901403075282</v>
       </c>
       <c r="C27">
-        <v>1.531736842567787</v>
+        <v>1.51649868843966</v>
       </c>
       <c r="D27">
-        <v>1.912236842567787</v>
+        <v>1.91365868843966</v>
       </c>
       <c r="E27">
-        <v>-0.3135</v>
+        <v>-0.29684</v>
       </c>
       <c r="F27">
-        <v>0.4165</v>
+        <v>0.43316</v>
       </c>
       <c r="G27">
         <v>0.036</v>
@@ -3483,45 +3483,45 @@
         <v>0.217</v>
       </c>
       <c r="M27">
-        <v>0.0215747</v>
+        <v>0.02317406</v>
       </c>
       <c r="N27">
-        <v>0.1954253</v>
+        <v>0.19382594</v>
       </c>
       <c r="O27">
-        <v>0.04885632499999999</v>
+        <v>0.04845648499999999</v>
       </c>
       <c r="P27">
-        <v>0.146568975</v>
+        <v>0.145369455</v>
       </c>
       <c r="Q27">
-        <v>0.199568975</v>
+        <v>0.198369455</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2265027276838611</v>
+        <v>0.2284562706858489</v>
       </c>
       <c r="T27">
-        <v>1.105155387785786</v>
+        <v>1.117103013599687</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>10.05807728496804</v>
+        <v>9.363918104984624</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1794901403075282</v>
+        <v>0.1790719848521604</v>
       </c>
       <c r="C28">
-        <v>1.51649868843966</v>
+        <v>1.505843002258281</v>
       </c>
       <c r="D28">
-        <v>1.91365868843966</v>
+        <v>1.919663002258281</v>
       </c>
       <c r="E28">
-        <v>-0.29684</v>
+        <v>-0.28018</v>
       </c>
       <c r="F28">
-        <v>0.43316</v>
+        <v>0.44982</v>
       </c>
       <c r="G28">
         <v>0.036</v>
@@ -3565,28 +3565,28 @@
         <v>0.217</v>
       </c>
       <c r="M28">
-        <v>0.02317406</v>
+        <v>0.02406537</v>
       </c>
       <c r="N28">
-        <v>0.19382594</v>
+        <v>0.19293463</v>
       </c>
       <c r="O28">
-        <v>0.04845648499999999</v>
+        <v>0.04823365749999999</v>
       </c>
       <c r="P28">
-        <v>0.145369455</v>
+        <v>0.1447009725</v>
       </c>
       <c r="Q28">
-        <v>0.198369455</v>
+        <v>0.1977009725</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2284562706858489</v>
+        <v>0.2304633354139184</v>
       </c>
       <c r="T28">
-        <v>1.117103013599687</v>
+        <v>1.129377971627666</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.363918104984624</v>
+        <v>9.017106323318528</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1790719848521604</v>
+        <v>0.1786538293967927</v>
       </c>
       <c r="C29">
-        <v>1.505843002258281</v>
+        <v>1.495225113054082</v>
       </c>
       <c r="D29">
-        <v>1.919663002258281</v>
+        <v>1.925705113054082</v>
       </c>
       <c r="E29">
-        <v>-0.28018</v>
+        <v>-0.26352</v>
       </c>
       <c r="F29">
-        <v>0.44982</v>
+        <v>0.46648</v>
       </c>
       <c r="G29">
         <v>0.036</v>
@@ -3647,28 +3647,28 @@
         <v>0.217</v>
       </c>
       <c r="M29">
-        <v>0.02406537</v>
+        <v>0.02495668</v>
       </c>
       <c r="N29">
-        <v>0.19293463</v>
+        <v>0.19204332</v>
       </c>
       <c r="O29">
-        <v>0.04823365749999999</v>
+        <v>0.04801082999999999</v>
       </c>
       <c r="P29">
-        <v>0.1447009725</v>
+        <v>0.14403249</v>
       </c>
       <c r="Q29">
-        <v>0.1977009725</v>
+        <v>0.1970324899999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2304633354139184</v>
+        <v>0.2325261519399899</v>
       </c>
       <c r="T29">
-        <v>1.129377971627666</v>
+        <v>1.141993900711979</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.017106323318528</v>
+        <v>8.695066811771436</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1786538293967927</v>
+        <v>0.178235673941425</v>
       </c>
       <c r="C30">
-        <v>1.495225113054082</v>
+        <v>1.484645378850209</v>
       </c>
       <c r="D30">
-        <v>1.925705113054082</v>
+        <v>1.931785378850209</v>
       </c>
       <c r="E30">
-        <v>-0.26352</v>
+        <v>-0.24686</v>
       </c>
       <c r="F30">
-        <v>0.46648</v>
+        <v>0.48314</v>
       </c>
       <c r="G30">
         <v>0.036</v>
@@ -3729,28 +3729,28 @@
         <v>0.217</v>
       </c>
       <c r="M30">
-        <v>0.02495668</v>
+        <v>0.02584799</v>
       </c>
       <c r="N30">
-        <v>0.19204332</v>
+        <v>0.19115201</v>
       </c>
       <c r="O30">
-        <v>0.04801082999999999</v>
+        <v>0.0477880025</v>
       </c>
       <c r="P30">
-        <v>0.14403249</v>
+        <v>0.1433640075</v>
       </c>
       <c r="Q30">
-        <v>0.1970324899999999</v>
+        <v>0.1963640075</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2325261519399899</v>
+        <v>0.234647075973838</v>
       </c>
       <c r="T30">
-        <v>1.141993900711979</v>
+        <v>1.154965208080357</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.695066811771436</v>
+        <v>8.395236921710353</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1782356739414249</v>
+        <v>0.1778175184860573</v>
       </c>
       <c r="C31">
-        <v>1.48464537885021</v>
+        <v>1.474104162205852</v>
       </c>
       <c r="D31">
-        <v>1.93178537885021</v>
+        <v>1.937904162205852</v>
       </c>
       <c r="E31">
-        <v>-0.24686</v>
+        <v>-0.2302</v>
       </c>
       <c r="F31">
-        <v>0.48314</v>
+        <v>0.4998</v>
       </c>
       <c r="G31">
         <v>0.036</v>
@@ -3811,28 +3811,28 @@
         <v>0.217</v>
       </c>
       <c r="M31">
-        <v>0.02584799</v>
+        <v>0.0267393</v>
       </c>
       <c r="N31">
-        <v>0.19115201</v>
+        <v>0.1902607</v>
       </c>
       <c r="O31">
-        <v>0.0477880025</v>
+        <v>0.04756517499999999</v>
       </c>
       <c r="P31">
-        <v>0.1433640075</v>
+        <v>0.142695525</v>
       </c>
       <c r="Q31">
-        <v>0.1963640075</v>
+        <v>0.195695525</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.234647075973838</v>
+        <v>0.2368285978372247</v>
       </c>
       <c r="T31">
-        <v>1.154965208080357</v>
+        <v>1.168307124230688</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.395236921710353</v>
+        <v>8.115395690986675</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1778175184860573</v>
+        <v>0.1773993630306895</v>
       </c>
       <c r="C32">
-        <v>1.474104162205852</v>
+        <v>1.463601830288313</v>
       </c>
       <c r="D32">
-        <v>1.937904162205852</v>
+        <v>1.944061830288313</v>
       </c>
       <c r="E32">
-        <v>-0.2302</v>
+        <v>-0.2135400000000001</v>
       </c>
       <c r="F32">
-        <v>0.4998</v>
+        <v>0.5164599999999999</v>
       </c>
       <c r="G32">
         <v>0.036</v>
@@ -3893,28 +3893,28 @@
         <v>0.217</v>
       </c>
       <c r="M32">
-        <v>0.0267393</v>
+        <v>0.02763061</v>
       </c>
       <c r="N32">
-        <v>0.1902607</v>
+        <v>0.18936939</v>
       </c>
       <c r="O32">
-        <v>0.04756517499999999</v>
+        <v>0.04734234749999999</v>
       </c>
       <c r="P32">
-        <v>0.142695525</v>
+        <v>0.1420270425</v>
       </c>
       <c r="Q32">
-        <v>0.195695525</v>
+        <v>0.1950270425</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2368285978372247</v>
+        <v>0.2390733522183906</v>
       </c>
       <c r="T32">
-        <v>1.168307124230688</v>
+        <v>1.182035762588276</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.115395690986675</v>
+        <v>7.853608733212911</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1773993630306895</v>
+        <v>0.1771732075753218</v>
       </c>
       <c r="C33">
-        <v>1.463601830288313</v>
+        <v>1.450288480618364</v>
       </c>
       <c r="D33">
-        <v>1.944061830288313</v>
+        <v>1.947408480618364</v>
       </c>
       <c r="E33">
-        <v>-0.2135400000000001</v>
+        <v>-0.1968799999999999</v>
       </c>
       <c r="F33">
-        <v>0.5164599999999999</v>
+        <v>0.53312</v>
       </c>
       <c r="G33">
         <v>0.036</v>
@@ -3975,45 +3975,45 @@
         <v>0.217</v>
       </c>
       <c r="M33">
-        <v>0.02763061</v>
+        <v>0.028948416</v>
       </c>
       <c r="N33">
-        <v>0.18936939</v>
+        <v>0.188051584</v>
       </c>
       <c r="O33">
-        <v>0.04734234749999999</v>
+        <v>0.04701289599999999</v>
       </c>
       <c r="P33">
-        <v>0.1420270425</v>
+        <v>0.141038688</v>
       </c>
       <c r="Q33">
-        <v>0.1950270425</v>
+        <v>0.194038688</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2390733522183906</v>
+        <v>0.241384128787238</v>
       </c>
       <c r="T33">
-        <v>1.182035762588276</v>
+        <v>1.196168184426969</v>
       </c>
       <c r="U33">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.853608733212911</v>
+        <v>7.496092359595771</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1771732075753218</v>
+        <v>0.1767610521199541</v>
       </c>
       <c r="C34">
-        <v>1.450288480618364</v>
+        <v>1.439757287741729</v>
       </c>
       <c r="D34">
-        <v>1.947408480618364</v>
+        <v>1.953537287741729</v>
       </c>
       <c r="E34">
-        <v>-0.1968799999999999</v>
+        <v>-0.1802199999999999</v>
       </c>
       <c r="F34">
-        <v>0.53312</v>
+        <v>0.54978</v>
       </c>
       <c r="G34">
         <v>0.036</v>
@@ -4057,28 +4057,28 @@
         <v>0.217</v>
       </c>
       <c r="M34">
-        <v>0.028948416</v>
+        <v>0.029853054</v>
       </c>
       <c r="N34">
-        <v>0.188051584</v>
+        <v>0.187146946</v>
       </c>
       <c r="O34">
-        <v>0.04701289599999999</v>
+        <v>0.0467867365</v>
       </c>
       <c r="P34">
-        <v>0.141038688</v>
+        <v>0.1403602095</v>
       </c>
       <c r="Q34">
-        <v>0.194038688</v>
+        <v>0.1933602095</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.241384128787238</v>
+        <v>0.2437638837611256</v>
       </c>
       <c r="T34">
-        <v>1.196168184426969</v>
+        <v>1.21072246960413</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.496092359595771</v>
+        <v>7.268938045668626</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1767610521199541</v>
+        <v>0.1763488966645864</v>
       </c>
       <c r="C35">
-        <v>1.439757287741729</v>
+        <v>1.429264793335252</v>
       </c>
       <c r="D35">
-        <v>1.953537287741729</v>
+        <v>1.959704793335252</v>
       </c>
       <c r="E35">
-        <v>-0.1802199999999999</v>
+        <v>-0.1635599999999999</v>
       </c>
       <c r="F35">
-        <v>0.54978</v>
+        <v>0.5664400000000001</v>
       </c>
       <c r="G35">
         <v>0.036</v>
@@ -4139,28 +4139,28 @@
         <v>0.217</v>
       </c>
       <c r="M35">
-        <v>0.029853054</v>
+        <v>0.030757692</v>
       </c>
       <c r="N35">
-        <v>0.187146946</v>
+        <v>0.186242308</v>
       </c>
       <c r="O35">
-        <v>0.0467867365</v>
+        <v>0.04656057699999999</v>
       </c>
       <c r="P35">
-        <v>0.1403602095</v>
+        <v>0.139681731</v>
       </c>
       <c r="Q35">
-        <v>0.1933602095</v>
+        <v>0.192681731</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2437638837611256</v>
+        <v>0.2462157525221006</v>
       </c>
       <c r="T35">
-        <v>1.21072246960413</v>
+        <v>1.225717793726054</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.268938045668626</v>
+        <v>7.055145750207783</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1763488966645864</v>
+        <v>0.1759367412092187</v>
       </c>
       <c r="C36">
-        <v>1.429264793335252</v>
+        <v>1.418811365084155</v>
       </c>
       <c r="D36">
-        <v>1.959704793335252</v>
+        <v>1.965911365084155</v>
       </c>
       <c r="E36">
-        <v>-0.1635599999999999</v>
+        <v>-0.1468999999999999</v>
       </c>
       <c r="F36">
-        <v>0.5664400000000001</v>
+        <v>0.5831000000000001</v>
       </c>
       <c r="G36">
         <v>0.036</v>
@@ -4221,28 +4221,28 @@
         <v>0.217</v>
       </c>
       <c r="M36">
-        <v>0.030757692</v>
+        <v>0.03166233</v>
       </c>
       <c r="N36">
-        <v>0.186242308</v>
+        <v>0.18533767</v>
       </c>
       <c r="O36">
-        <v>0.04656057699999999</v>
+        <v>0.04633441749999999</v>
       </c>
       <c r="P36">
-        <v>0.139681731</v>
+        <v>0.1390032525</v>
       </c>
       <c r="Q36">
-        <v>0.192681731</v>
+        <v>0.1920032524999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2462157525221006</v>
+        <v>0.2487430633987979</v>
       </c>
       <c r="T36">
-        <v>1.225717793726054</v>
+        <v>1.241174512436344</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.055145750207783</v>
+        <v>6.853570157344704</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1759367412092187</v>
+        <v>0.1755245857538509</v>
       </c>
       <c r="C37">
-        <v>1.418811365084155</v>
+        <v>1.408397375346437</v>
       </c>
       <c r="D37">
-        <v>1.965911365084155</v>
+        <v>1.972157375346437</v>
       </c>
       <c r="E37">
-        <v>-0.1468999999999999</v>
+        <v>-0.1302399999999999</v>
       </c>
       <c r="F37">
-        <v>0.5831000000000001</v>
+        <v>0.5997600000000001</v>
       </c>
       <c r="G37">
         <v>0.036</v>
@@ -4303,28 +4303,28 @@
         <v>0.217</v>
       </c>
       <c r="M37">
-        <v>0.03166233</v>
+        <v>0.032566968</v>
       </c>
       <c r="N37">
-        <v>0.18533767</v>
+        <v>0.184433032</v>
       </c>
       <c r="O37">
-        <v>0.04633441749999999</v>
+        <v>0.04610825799999999</v>
       </c>
       <c r="P37">
-        <v>0.1390032525</v>
+        <v>0.138324774</v>
       </c>
       <c r="Q37">
-        <v>0.1920032524999999</v>
+        <v>0.191324774</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2487430633987979</v>
+        <v>0.2513493527403921</v>
       </c>
       <c r="T37">
-        <v>1.241174512436344</v>
+        <v>1.257114253606332</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.853570157344704</v>
+        <v>6.663193208529574</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1755245857538509</v>
+        <v>0.1751124302984832</v>
       </c>
       <c r="C38">
-        <v>1.408397375346437</v>
+        <v>1.39802320122734</v>
       </c>
       <c r="D38">
-        <v>1.972157375346437</v>
+        <v>1.97844320122734</v>
       </c>
       <c r="E38">
-        <v>-0.13024</v>
+        <v>-0.11358</v>
       </c>
       <c r="F38">
-        <v>0.59976</v>
+        <v>0.61642</v>
       </c>
       <c r="G38">
         <v>0.036</v>
@@ -4385,28 +4385,28 @@
         <v>0.217</v>
       </c>
       <c r="M38">
-        <v>0.032566968</v>
+        <v>0.033471606</v>
       </c>
       <c r="N38">
-        <v>0.184433032</v>
+        <v>0.183528394</v>
       </c>
       <c r="O38">
-        <v>0.04610825799999999</v>
+        <v>0.0458820985</v>
       </c>
       <c r="P38">
-        <v>0.138324774</v>
+        <v>0.1376462955</v>
       </c>
       <c r="Q38">
-        <v>0.191324774</v>
+        <v>0.1906462955</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2513493527403921</v>
+        <v>0.2540383814261638</v>
       </c>
       <c r="T38">
-        <v>1.257114253606332</v>
+        <v>1.273560018305525</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.663193208529574</v>
+        <v>6.483106905596343</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1751124302984832</v>
+        <v>0.1747002748431155</v>
       </c>
       <c r="C39">
-        <v>1.39802320122734</v>
+        <v>1.387689224655245</v>
       </c>
       <c r="D39">
-        <v>1.97844320122734</v>
+        <v>1.984769224655246</v>
       </c>
       <c r="E39">
-        <v>-0.11358</v>
+        <v>-0.09692000000000001</v>
       </c>
       <c r="F39">
-        <v>0.61642</v>
+        <v>0.63308</v>
       </c>
       <c r="G39">
         <v>0.036</v>
@@ -4467,28 +4467,28 @@
         <v>0.217</v>
       </c>
       <c r="M39">
-        <v>0.033471606</v>
+        <v>0.034376244</v>
       </c>
       <c r="N39">
-        <v>0.183528394</v>
+        <v>0.182623756</v>
       </c>
       <c r="O39">
-        <v>0.0458820985</v>
+        <v>0.04565593899999999</v>
       </c>
       <c r="P39">
-        <v>0.1376462955</v>
+        <v>0.136967817</v>
       </c>
       <c r="Q39">
-        <v>0.1906462955</v>
+        <v>0.189967817</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2540383814261638</v>
+        <v>0.2568141529727669</v>
       </c>
       <c r="T39">
-        <v>1.273560018305525</v>
+        <v>1.290536291543402</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.483106905596343</v>
+        <v>6.312498829133281</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1747002748431155</v>
+        <v>0.1742881193877478</v>
       </c>
       <c r="C40">
-        <v>1.387689224655245</v>
+        <v>1.37739583245903</v>
       </c>
       <c r="D40">
-        <v>1.984769224655246</v>
+        <v>1.99113583245903</v>
       </c>
       <c r="E40">
-        <v>-0.09692000000000001</v>
+        <v>-0.08026</v>
       </c>
       <c r="F40">
-        <v>0.63308</v>
+        <v>0.64974</v>
       </c>
       <c r="G40">
         <v>0.036</v>
@@ -4549,28 +4549,28 @@
         <v>0.217</v>
       </c>
       <c r="M40">
-        <v>0.034376244</v>
+        <v>0.035280882</v>
       </c>
       <c r="N40">
-        <v>0.182623756</v>
+        <v>0.181719118</v>
       </c>
       <c r="O40">
-        <v>0.04565593899999999</v>
+        <v>0.04542977949999999</v>
       </c>
       <c r="P40">
-        <v>0.136967817</v>
+        <v>0.1362893385</v>
       </c>
       <c r="Q40">
-        <v>0.189967817</v>
+        <v>0.1892893385</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2568141529727669</v>
+        <v>0.2596809334225373</v>
       </c>
       <c r="T40">
-        <v>1.290536291543402</v>
+        <v>1.308069163903832</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.312498829133281</v>
+        <v>6.150639884796529</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1742881193877478</v>
+        <v>0.17417596393238</v>
       </c>
       <c r="C41">
-        <v>1.37739583245903</v>
+        <v>1.362475385091376</v>
       </c>
       <c r="D41">
-        <v>1.99113583245903</v>
+        <v>1.992875385091376</v>
       </c>
       <c r="E41">
-        <v>-0.08026</v>
+        <v>-0.06359999999999999</v>
       </c>
       <c r="F41">
-        <v>0.64974</v>
+        <v>0.6664</v>
       </c>
       <c r="G41">
         <v>0.036</v>
@@ -4631,45 +4631,45 @@
         <v>0.217</v>
       </c>
       <c r="M41">
-        <v>0.035280882</v>
+        <v>0.03685192</v>
       </c>
       <c r="N41">
-        <v>0.181719118</v>
+        <v>0.18014808</v>
       </c>
       <c r="O41">
-        <v>0.04542977949999999</v>
+        <v>0.04503701999999999</v>
       </c>
       <c r="P41">
-        <v>0.1362893385</v>
+        <v>0.13511106</v>
       </c>
       <c r="Q41">
-        <v>0.1892893385</v>
+        <v>0.18811106</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2596809334225373</v>
+        <v>0.2626432732206334</v>
       </c>
       <c r="T41">
-        <v>1.308069163903832</v>
+        <v>1.326186465342943</v>
       </c>
       <c r="U41">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>6.150639884796529</v>
+        <v>5.888431321895846</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.17417596393238</v>
+        <v>0.1737713084770123</v>
       </c>
       <c r="C42">
-        <v>1.362475385091376</v>
+        <v>1.352117015558725</v>
       </c>
       <c r="D42">
-        <v>1.992875385091376</v>
+        <v>1.999177015558726</v>
       </c>
       <c r="E42">
-        <v>-0.06359999999999999</v>
+        <v>-0.04693999999999998</v>
       </c>
       <c r="F42">
-        <v>0.6664</v>
+        <v>0.68306</v>
       </c>
       <c r="G42">
         <v>0.036</v>
@@ -4713,28 +4713,28 @@
         <v>0.217</v>
       </c>
       <c r="M42">
-        <v>0.03685192</v>
+        <v>0.037773218</v>
       </c>
       <c r="N42">
-        <v>0.18014808</v>
+        <v>0.179226782</v>
       </c>
       <c r="O42">
-        <v>0.04503701999999999</v>
+        <v>0.04480669549999999</v>
       </c>
       <c r="P42">
-        <v>0.13511106</v>
+        <v>0.1344200865</v>
       </c>
       <c r="Q42">
-        <v>0.18811106</v>
+        <v>0.1874200865</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2626432732206334</v>
+        <v>0.26570603131697</v>
       </c>
       <c r="T42">
-        <v>1.326186465342943</v>
+        <v>1.34491791259355</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.888431321895846</v>
+        <v>5.744811045752044</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1737713084770123</v>
+        <v>0.1733666530216446</v>
       </c>
       <c r="C43">
-        <v>1.352117015558725</v>
+        <v>1.341798624956083</v>
       </c>
       <c r="D43">
-        <v>1.999177015558726</v>
+        <v>2.005518624956083</v>
       </c>
       <c r="E43">
-        <v>-0.04693999999999998</v>
+        <v>-0.03027999999999997</v>
       </c>
       <c r="F43">
-        <v>0.68306</v>
+        <v>0.69972</v>
       </c>
       <c r="G43">
         <v>0.036</v>
@@ -4795,28 +4795,28 @@
         <v>0.217</v>
       </c>
       <c r="M43">
-        <v>0.037773218</v>
+        <v>0.03869451600000001</v>
       </c>
       <c r="N43">
-        <v>0.179226782</v>
+        <v>0.178305484</v>
       </c>
       <c r="O43">
-        <v>0.04480669549999999</v>
+        <v>0.04457637099999999</v>
       </c>
       <c r="P43">
-        <v>0.1344200865</v>
+        <v>0.133729113</v>
       </c>
       <c r="Q43">
-        <v>0.1874200865</v>
+        <v>0.1867291129999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.26570603131697</v>
+        <v>0.2688744017614562</v>
       </c>
       <c r="T43">
-        <v>1.34491791259355</v>
+        <v>1.364295271818315</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.744811045752044</v>
+        <v>5.608029830376996</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1733666530216446</v>
+        <v>0.1729619975662769</v>
       </c>
       <c r="C44">
-        <v>1.341798624956082</v>
+        <v>1.331520594946819</v>
       </c>
       <c r="D44">
-        <v>2.005518624956082</v>
+        <v>2.011900594946819</v>
       </c>
       <c r="E44">
-        <v>-0.03028000000000008</v>
+        <v>-0.01362000000000008</v>
       </c>
       <c r="F44">
-        <v>0.6997199999999999</v>
+        <v>0.7163799999999999</v>
       </c>
       <c r="G44">
         <v>0.036</v>
@@ -4877,28 +4877,28 @@
         <v>0.217</v>
       </c>
       <c r="M44">
-        <v>0.038694516</v>
+        <v>0.039615814</v>
       </c>
       <c r="N44">
-        <v>0.178305484</v>
+        <v>0.177384186</v>
       </c>
       <c r="O44">
-        <v>0.04457637099999999</v>
+        <v>0.04434604649999999</v>
       </c>
       <c r="P44">
-        <v>0.133729113</v>
+        <v>0.1330381395</v>
       </c>
       <c r="Q44">
-        <v>0.1867291129999999</v>
+        <v>0.1860381395</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2688744017614562</v>
+        <v>0.2721539430987314</v>
       </c>
       <c r="T44">
-        <v>1.364295271818315</v>
+        <v>1.384352538384301</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.608029830376997</v>
+        <v>5.477610531996136</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1729619975662769</v>
+        <v>0.1725573421109091</v>
       </c>
       <c r="C45">
-        <v>1.331520594946819</v>
+        <v>1.321283312067935</v>
       </c>
       <c r="D45">
-        <v>2.011900594946819</v>
+        <v>2.018323312067935</v>
       </c>
       <c r="E45">
-        <v>-0.01362000000000008</v>
+        <v>0.003040000000000043</v>
       </c>
       <c r="F45">
-        <v>0.7163799999999999</v>
+        <v>0.73304</v>
       </c>
       <c r="G45">
         <v>0.036</v>
@@ -4959,28 +4959,28 @@
         <v>0.217</v>
       </c>
       <c r="M45">
-        <v>0.039615814</v>
+        <v>0.040537112</v>
       </c>
       <c r="N45">
-        <v>0.177384186</v>
+        <v>0.176462888</v>
       </c>
       <c r="O45">
-        <v>0.04434604649999999</v>
+        <v>0.044115722</v>
       </c>
       <c r="P45">
-        <v>0.1330381395</v>
+        <v>0.132347166</v>
       </c>
       <c r="Q45">
-        <v>0.1860381395</v>
+        <v>0.185347166</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2721539430987314</v>
+        <v>0.2755506109123377</v>
       </c>
       <c r="T45">
-        <v>1.384352538384301</v>
+        <v>1.405126135899071</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.477610531996136</v>
+        <v>5.353119383541679</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1725573421109091</v>
+        <v>0.1721526866555415</v>
       </c>
       <c r="C46">
-        <v>1.321283312067935</v>
+        <v>1.311087167808103</v>
       </c>
       <c r="D46">
-        <v>2.018323312067935</v>
+        <v>2.024787167808103</v>
       </c>
       <c r="E46">
-        <v>0.003040000000000043</v>
+        <v>0.01970000000000005</v>
       </c>
       <c r="F46">
-        <v>0.73304</v>
+        <v>0.7497</v>
       </c>
       <c r="G46">
         <v>0.036</v>
@@ -5041,28 +5041,28 @@
         <v>0.217</v>
       </c>
       <c r="M46">
-        <v>0.040537112</v>
+        <v>0.04145841</v>
       </c>
       <c r="N46">
-        <v>0.176462888</v>
+        <v>0.17554159</v>
       </c>
       <c r="O46">
-        <v>0.044115722</v>
+        <v>0.04388539749999999</v>
       </c>
       <c r="P46">
-        <v>0.132347166</v>
+        <v>0.1316561925</v>
       </c>
       <c r="Q46">
-        <v>0.185347166</v>
+        <v>0.1846561925</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2755506109123377</v>
+        <v>0.2790707939191662</v>
       </c>
       <c r="T46">
-        <v>1.405126135899071</v>
+        <v>1.426655136959833</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.353119383541679</v>
+        <v>5.23416117501853</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1721526866555415</v>
+        <v>0.1717480312001737</v>
       </c>
       <c r="C47">
-        <v>1.311087167808103</v>
+        <v>1.300932558687218</v>
       </c>
       <c r="D47">
-        <v>2.024787167808103</v>
+        <v>2.031292558687218</v>
       </c>
       <c r="E47">
-        <v>0.01970000000000005</v>
+        <v>0.03636000000000006</v>
       </c>
       <c r="F47">
-        <v>0.7497</v>
+        <v>0.76636</v>
       </c>
       <c r="G47">
         <v>0.036</v>
@@ -5123,28 +5123,28 @@
         <v>0.217</v>
       </c>
       <c r="M47">
-        <v>0.04145841</v>
+        <v>0.042379708</v>
       </c>
       <c r="N47">
-        <v>0.17554159</v>
+        <v>0.174620292</v>
       </c>
       <c r="O47">
-        <v>0.04388539749999999</v>
+        <v>0.04365507299999999</v>
       </c>
       <c r="P47">
-        <v>0.1316561925</v>
+        <v>0.130965219</v>
       </c>
       <c r="Q47">
-        <v>0.1846561925</v>
+        <v>0.183965219</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2790707939191662</v>
+        <v>0.2827213540743957</v>
       </c>
       <c r="T47">
-        <v>1.426655136959833</v>
+        <v>1.448981508430253</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.23416117501853</v>
+        <v>5.120375062518127</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1717480312001737</v>
+        <v>0.171343375744806</v>
       </c>
       <c r="C48">
-        <v>1.300932558687218</v>
+        <v>1.290819886337476</v>
       </c>
       <c r="D48">
-        <v>2.031292558687218</v>
+        <v>2.037839886337476</v>
       </c>
       <c r="E48">
-        <v>0.03636000000000006</v>
+        <v>0.05302000000000007</v>
       </c>
       <c r="F48">
-        <v>0.76636</v>
+        <v>0.78302</v>
       </c>
       <c r="G48">
         <v>0.036</v>
@@ -5205,28 +5205,28 @@
         <v>0.217</v>
       </c>
       <c r="M48">
-        <v>0.042379708</v>
+        <v>0.043301006</v>
       </c>
       <c r="N48">
-        <v>0.174620292</v>
+        <v>0.173698994</v>
       </c>
       <c r="O48">
-        <v>0.04365507299999999</v>
+        <v>0.04342474849999999</v>
       </c>
       <c r="P48">
-        <v>0.130965219</v>
+        <v>0.1302742455</v>
       </c>
       <c r="Q48">
-        <v>0.183965219</v>
+        <v>0.1832742455</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2827213540743957</v>
+        <v>0.286509671216615</v>
       </c>
       <c r="T48">
-        <v>1.448981508430253</v>
+        <v>1.472150384484462</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.120375062518127</v>
+        <v>5.011430912251783</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.171343375744806</v>
+        <v>0.1709387202894383</v>
       </c>
       <c r="C49">
-        <v>1.290819886337476</v>
+        <v>1.280749557586032</v>
       </c>
       <c r="D49">
-        <v>2.037839886337476</v>
+        <v>2.044429557586032</v>
       </c>
       <c r="E49">
-        <v>0.05302000000000007</v>
+        <v>0.06968000000000008</v>
       </c>
       <c r="F49">
-        <v>0.78302</v>
+        <v>0.7996800000000001</v>
       </c>
       <c r="G49">
         <v>0.036</v>
@@ -5287,28 +5287,28 @@
         <v>0.217</v>
       </c>
       <c r="M49">
-        <v>0.043301006</v>
+        <v>0.044222304</v>
       </c>
       <c r="N49">
-        <v>0.173698994</v>
+        <v>0.172777696</v>
       </c>
       <c r="O49">
-        <v>0.04342474849999999</v>
+        <v>0.043194424</v>
       </c>
       <c r="P49">
-        <v>0.1302742455</v>
+        <v>0.129583272</v>
       </c>
       <c r="Q49">
-        <v>0.1832742455</v>
+        <v>0.182583272</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.286509671216615</v>
+        <v>0.2904436928643043</v>
       </c>
       <c r="T49">
-        <v>1.472150384484462</v>
+        <v>1.496210371156141</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.011430912251783</v>
+        <v>4.907026101579872</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1709387202894383</v>
+        <v>0.1705340648340705</v>
       </c>
       <c r="C50">
-        <v>1.280749557586032</v>
+        <v>1.270721984539268</v>
       </c>
       <c r="D50">
-        <v>2.044429557586032</v>
+        <v>2.051061984539268</v>
       </c>
       <c r="E50">
-        <v>0.06967999999999996</v>
+        <v>0.08633999999999997</v>
       </c>
       <c r="F50">
-        <v>0.7996799999999999</v>
+        <v>0.81634</v>
       </c>
       <c r="G50">
         <v>0.036</v>
@@ -5369,28 +5369,28 @@
         <v>0.217</v>
       </c>
       <c r="M50">
-        <v>0.044222304</v>
+        <v>0.045143602</v>
       </c>
       <c r="N50">
-        <v>0.172777696</v>
+        <v>0.171856398</v>
       </c>
       <c r="O50">
-        <v>0.043194424</v>
+        <v>0.04296409949999999</v>
       </c>
       <c r="P50">
-        <v>0.129583272</v>
+        <v>0.1288922985</v>
       </c>
       <c r="Q50">
-        <v>0.182583272</v>
+        <v>0.1818922985</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2904436928643043</v>
+        <v>0.2945319898707265</v>
       </c>
       <c r="T50">
-        <v>1.496210371156141</v>
+        <v>1.521213886716906</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.907026101579872</v>
+        <v>4.806882711751712</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1705340648340705</v>
+        <v>0.1701294093787028</v>
       </c>
       <c r="C51">
-        <v>1.270721984539268</v>
+        <v>1.260737584668704</v>
       </c>
       <c r="D51">
-        <v>2.051061984539268</v>
+        <v>2.057737584668704</v>
       </c>
       <c r="E51">
-        <v>0.08633999999999997</v>
+        <v>0.103</v>
       </c>
       <c r="F51">
-        <v>0.81634</v>
+        <v>0.833</v>
       </c>
       <c r="G51">
         <v>0.036</v>
@@ -5451,28 +5451,28 @@
         <v>0.217</v>
       </c>
       <c r="M51">
-        <v>0.045143602</v>
+        <v>0.0460649</v>
       </c>
       <c r="N51">
-        <v>0.171856398</v>
+        <v>0.1709351</v>
       </c>
       <c r="O51">
-        <v>0.04296409949999999</v>
+        <v>0.04273377499999999</v>
       </c>
       <c r="P51">
-        <v>0.1288922985</v>
+        <v>0.128201325</v>
       </c>
       <c r="Q51">
-        <v>0.1818922985</v>
+        <v>0.181201325</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2945319898707265</v>
+        <v>0.2987838187574057</v>
       </c>
       <c r="T51">
-        <v>1.521213886716906</v>
+        <v>1.547217542900101</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.806882711751712</v>
+        <v>4.710745057516677</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1701294093787028</v>
+        <v>0.1697247539233351</v>
       </c>
       <c r="C52">
-        <v>1.260737584668704</v>
+        <v>1.250796780898591</v>
       </c>
       <c r="D52">
-        <v>2.057737584668704</v>
+        <v>2.064456780898591</v>
       </c>
       <c r="E52">
-        <v>0.103</v>
+        <v>0.11966</v>
       </c>
       <c r="F52">
-        <v>0.833</v>
+        <v>0.84966</v>
       </c>
       <c r="G52">
         <v>0.036</v>
@@ -5533,28 +5533,28 @@
         <v>0.217</v>
       </c>
       <c r="M52">
-        <v>0.0460649</v>
+        <v>0.046986198</v>
       </c>
       <c r="N52">
-        <v>0.1709351</v>
+        <v>0.170013802</v>
       </c>
       <c r="O52">
-        <v>0.04273377499999999</v>
+        <v>0.04250345049999999</v>
       </c>
       <c r="P52">
-        <v>0.128201325</v>
+        <v>0.1275103515</v>
       </c>
       <c r="Q52">
-        <v>0.181201325</v>
+        <v>0.1805103515</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2987838187574057</v>
+        <v>0.3032091916802757</v>
       </c>
       <c r="T52">
-        <v>1.547217542900101</v>
+        <v>1.574282572805059</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.710745057516677</v>
+        <v>4.61837750736929</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1697247539233351</v>
+        <v>0.1693200984679674</v>
       </c>
       <c r="C53">
-        <v>1.250796780898591</v>
+        <v>1.240900001695231</v>
       </c>
       <c r="D53">
-        <v>2.064456780898591</v>
+        <v>2.071220001695231</v>
       </c>
       <c r="E53">
-        <v>0.11966</v>
+        <v>0.13632</v>
       </c>
       <c r="F53">
-        <v>0.84966</v>
+        <v>0.86632</v>
       </c>
       <c r="G53">
         <v>0.036</v>
@@ -5615,28 +5615,28 @@
         <v>0.217</v>
       </c>
       <c r="M53">
-        <v>0.046986198</v>
+        <v>0.047907496</v>
       </c>
       <c r="N53">
-        <v>0.170013802</v>
+        <v>0.169092504</v>
       </c>
       <c r="O53">
-        <v>0.04250345049999999</v>
+        <v>0.04227312599999999</v>
       </c>
       <c r="P53">
-        <v>0.1275103515</v>
+        <v>0.126819378</v>
       </c>
       <c r="Q53">
-        <v>0.1805103515</v>
+        <v>0.179819378</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3032091916802757</v>
+        <v>0.3078189551415987</v>
       </c>
       <c r="T53">
-        <v>1.574282572805059</v>
+        <v>1.60247531228939</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.61837750736929</v>
+        <v>4.529562555304497</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1693200984679674</v>
+        <v>0.1699091930125997</v>
       </c>
       <c r="C54">
-        <v>1.240900001695231</v>
+        <v>1.214408784731246</v>
       </c>
       <c r="D54">
-        <v>2.071220001695231</v>
+        <v>2.061388784731246</v>
       </c>
       <c r="E54">
-        <v>0.13632</v>
+        <v>0.15298</v>
       </c>
       <c r="F54">
-        <v>0.86632</v>
+        <v>0.88298</v>
       </c>
       <c r="G54">
         <v>0.036</v>
@@ -5697,45 +5697,45 @@
         <v>0.217</v>
       </c>
       <c r="M54">
-        <v>0.047907496</v>
+        <v>0.051036244</v>
       </c>
       <c r="N54">
-        <v>0.169092504</v>
+        <v>0.165963756</v>
       </c>
       <c r="O54">
-        <v>0.04227312599999999</v>
+        <v>0.04149093899999999</v>
       </c>
       <c r="P54">
-        <v>0.126819378</v>
+        <v>0.124472817</v>
       </c>
       <c r="Q54">
-        <v>0.179819378</v>
+        <v>0.177472817</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3078189551415987</v>
+        <v>0.3126248787502121</v>
       </c>
       <c r="T54">
-        <v>1.60247531228939</v>
+        <v>1.631867742815608</v>
       </c>
       <c r="U54">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.529562555304497</v>
+        <v>4.251880291190707</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1699091930125997</v>
+        <v>0.1695232875572319</v>
       </c>
       <c r="C55">
-        <v>1.214408784731246</v>
+        <v>1.204178464974697</v>
       </c>
       <c r="D55">
-        <v>2.061388784731246</v>
+        <v>2.067818464974697</v>
       </c>
       <c r="E55">
-        <v>0.15298</v>
+        <v>0.16964</v>
       </c>
       <c r="F55">
-        <v>0.88298</v>
+        <v>0.89964</v>
       </c>
       <c r="G55">
         <v>0.036</v>
@@ -5779,28 +5779,28 @@
         <v>0.217</v>
       </c>
       <c r="M55">
-        <v>0.051036244</v>
+        <v>0.05199919200000001</v>
       </c>
       <c r="N55">
-        <v>0.165963756</v>
+        <v>0.165000808</v>
       </c>
       <c r="O55">
-        <v>0.04149093899999999</v>
+        <v>0.04125020199999999</v>
       </c>
       <c r="P55">
-        <v>0.124472817</v>
+        <v>0.123750606</v>
       </c>
       <c r="Q55">
-        <v>0.177472817</v>
+        <v>0.176750606</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3126248787502121</v>
+        <v>0.3176397555591999</v>
       </c>
       <c r="T55">
-        <v>1.631867742815608</v>
+        <v>1.662538105103835</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.251880291190707</v>
+        <v>4.173141767279768</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1695232875572319</v>
+        <v>0.1691373821018642</v>
       </c>
       <c r="C56">
-        <v>1.204178464974697</v>
+        <v>1.193988380362433</v>
       </c>
       <c r="D56">
-        <v>2.067818464974697</v>
+        <v>2.074288380362433</v>
       </c>
       <c r="E56">
-        <v>0.16964</v>
+        <v>0.1863</v>
       </c>
       <c r="F56">
-        <v>0.89964</v>
+        <v>0.9163</v>
       </c>
       <c r="G56">
         <v>0.036</v>
@@ -5861,28 +5861,28 @@
         <v>0.217</v>
       </c>
       <c r="M56">
-        <v>0.05199919200000001</v>
+        <v>0.05296214</v>
       </c>
       <c r="N56">
-        <v>0.165000808</v>
+        <v>0.16403786</v>
       </c>
       <c r="O56">
-        <v>0.04125020199999999</v>
+        <v>0.04100946499999999</v>
       </c>
       <c r="P56">
-        <v>0.123750606</v>
+        <v>0.123028395</v>
       </c>
       <c r="Q56">
-        <v>0.176750606</v>
+        <v>0.176028395</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3176397555591999</v>
+        <v>0.3228775157819205</v>
       </c>
       <c r="T56">
-        <v>1.662538105103835</v>
+        <v>1.694571594604872</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.173141767279768</v>
+        <v>4.097266462420135</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1691373821018642</v>
+        <v>0.1687514766464965</v>
       </c>
       <c r="C57">
-        <v>1.193988380362433</v>
+        <v>1.183838909750293</v>
       </c>
       <c r="D57">
-        <v>2.074288380362433</v>
+        <v>2.080798909750293</v>
       </c>
       <c r="E57">
-        <v>0.1863</v>
+        <v>0.20296</v>
       </c>
       <c r="F57">
-        <v>0.9163</v>
+        <v>0.93296</v>
       </c>
       <c r="G57">
         <v>0.036</v>
@@ -5943,28 +5943,28 @@
         <v>0.217</v>
       </c>
       <c r="M57">
-        <v>0.05296214</v>
+        <v>0.053925088</v>
       </c>
       <c r="N57">
-        <v>0.16403786</v>
+        <v>0.163074912</v>
       </c>
       <c r="O57">
-        <v>0.04100946499999999</v>
+        <v>0.04076872799999999</v>
       </c>
       <c r="P57">
-        <v>0.123028395</v>
+        <v>0.122306184</v>
       </c>
       <c r="Q57">
-        <v>0.176028395</v>
+        <v>0.175306184</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3228775157819205</v>
+        <v>0.3283533560147647</v>
       </c>
       <c r="T57">
-        <v>1.694571594604872</v>
+        <v>1.728061151810502</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.097266462420135</v>
+        <v>4.024100989876919</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1687514766464965</v>
+        <v>0.1698618211911288</v>
       </c>
       <c r="C58">
-        <v>1.183838909750293</v>
+        <v>1.148555906349765</v>
       </c>
       <c r="D58">
-        <v>2.080798909750293</v>
+        <v>2.062175906349764</v>
       </c>
       <c r="E58">
-        <v>0.20296</v>
+        <v>0.21962</v>
       </c>
       <c r="F58">
-        <v>0.93296</v>
+        <v>0.94962</v>
       </c>
       <c r="G58">
         <v>0.036</v>
@@ -6025,45 +6025,45 @@
         <v>0.217</v>
       </c>
       <c r="M58">
-        <v>0.053925088</v>
+        <v>0.058211706</v>
       </c>
       <c r="N58">
-        <v>0.163074912</v>
+        <v>0.158788294</v>
       </c>
       <c r="O58">
-        <v>0.04076872799999999</v>
+        <v>0.03969707349999999</v>
       </c>
       <c r="P58">
-        <v>0.122306184</v>
+        <v>0.1190912205</v>
       </c>
       <c r="Q58">
-        <v>0.175306184</v>
+        <v>0.1720912205</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3283533560147647</v>
+        <v>0.3340838864909972</v>
       </c>
       <c r="T58">
-        <v>1.728061151810502</v>
+        <v>1.76310836283965</v>
       </c>
       <c r="U58">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>4.024100989876919</v>
+        <v>3.727772554887843</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1698618211911288</v>
+        <v>0.169502165735761</v>
       </c>
       <c r="C59">
-        <v>1.148555906349765</v>
+        <v>1.137891539572799</v>
       </c>
       <c r="D59">
-        <v>2.062175906349764</v>
+        <v>2.068171539572799</v>
       </c>
       <c r="E59">
-        <v>0.21962</v>
+        <v>0.23628</v>
       </c>
       <c r="F59">
-        <v>0.94962</v>
+        <v>0.96628</v>
       </c>
       <c r="G59">
         <v>0.036</v>
@@ -6107,28 +6107,28 @@
         <v>0.217</v>
       </c>
       <c r="M59">
-        <v>0.058211706</v>
+        <v>0.059232964</v>
       </c>
       <c r="N59">
-        <v>0.158788294</v>
+        <v>0.157767036</v>
       </c>
       <c r="O59">
-        <v>0.03969707349999999</v>
+        <v>0.03944175899999999</v>
       </c>
       <c r="P59">
-        <v>0.1190912205</v>
+        <v>0.118325277</v>
       </c>
       <c r="Q59">
-        <v>0.1720912205</v>
+        <v>0.171325277</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3340838864909972</v>
+        <v>0.3400872993708597</v>
       </c>
       <c r="T59">
-        <v>1.76310836283965</v>
+        <v>1.799824488679709</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.727772554887843</v>
+        <v>3.663500614286328</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1695021657357611</v>
+        <v>0.1691425102803933</v>
       </c>
       <c r="C60">
-        <v>1.137891539572799</v>
+        <v>1.127262138229764</v>
       </c>
       <c r="D60">
-        <v>2.068171539572798</v>
+        <v>2.074202138229764</v>
       </c>
       <c r="E60">
-        <v>0.2362799999999999</v>
+        <v>0.2529399999999999</v>
       </c>
       <c r="F60">
-        <v>0.9662799999999999</v>
+        <v>0.9829399999999999</v>
       </c>
       <c r="G60">
         <v>0.036</v>
@@ -6189,28 +6189,28 @@
         <v>0.217</v>
       </c>
       <c r="M60">
-        <v>0.05923296399999999</v>
+        <v>0.060254222</v>
       </c>
       <c r="N60">
-        <v>0.157767036</v>
+        <v>0.156745778</v>
       </c>
       <c r="O60">
-        <v>0.03944175899999999</v>
+        <v>0.03918644449999999</v>
       </c>
       <c r="P60">
-        <v>0.118325277</v>
+        <v>0.1175593335</v>
       </c>
       <c r="Q60">
-        <v>0.171325277</v>
+        <v>0.1705593335</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3400872993708596</v>
+        <v>0.3463835616594959</v>
       </c>
       <c r="T60">
-        <v>1.799824488679709</v>
+        <v>1.838331645048551</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.663500614286329</v>
+        <v>3.601407383535713</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1691425102803933</v>
+        <v>0.1687828548250256</v>
       </c>
       <c r="C61">
-        <v>1.127262138229764</v>
+        <v>1.116668009083154</v>
       </c>
       <c r="D61">
-        <v>2.074202138229764</v>
+        <v>2.080268009083154</v>
       </c>
       <c r="E61">
-        <v>0.2529399999999999</v>
+        <v>0.2696</v>
       </c>
       <c r="F61">
-        <v>0.9829399999999999</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="G61">
         <v>0.036</v>
@@ -6271,28 +6271,28 @@
         <v>0.217</v>
       </c>
       <c r="M61">
-        <v>0.060254222</v>
+        <v>0.06127547999999999</v>
       </c>
       <c r="N61">
-        <v>0.156745778</v>
+        <v>0.15572452</v>
       </c>
       <c r="O61">
-        <v>0.03918644449999999</v>
+        <v>0.03893112999999999</v>
       </c>
       <c r="P61">
-        <v>0.1175593335</v>
+        <v>0.11679339</v>
       </c>
       <c r="Q61">
-        <v>0.1705593335</v>
+        <v>0.16979339</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3463835616594959</v>
+        <v>0.352994637062564</v>
       </c>
       <c r="T61">
-        <v>1.838331645048551</v>
+        <v>1.878764159235836</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.601407383535713</v>
+        <v>3.541383927143451</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1687828548250256</v>
+        <v>0.1697041993696579</v>
       </c>
       <c r="C62">
-        <v>1.116668009083154</v>
+        <v>1.084539255067612</v>
       </c>
       <c r="D62">
-        <v>2.080268009083154</v>
+        <v>2.064799255067612</v>
       </c>
       <c r="E62">
-        <v>0.2696</v>
+        <v>0.28626</v>
       </c>
       <c r="F62">
-        <v>0.9995999999999999</v>
+        <v>1.01626</v>
       </c>
       <c r="G62">
         <v>0.036</v>
@@ -6353,45 +6353,45 @@
         <v>0.217</v>
       </c>
       <c r="M62">
-        <v>0.06127547999999999</v>
+        <v>0.065142266</v>
       </c>
       <c r="N62">
-        <v>0.15572452</v>
+        <v>0.151857734</v>
       </c>
       <c r="O62">
-        <v>0.03893112999999999</v>
+        <v>0.03796443349999999</v>
       </c>
       <c r="P62">
-        <v>0.11679339</v>
+        <v>0.1138933005</v>
       </c>
       <c r="Q62">
-        <v>0.16979339</v>
+        <v>0.1668933005</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.352994637062564</v>
+        <v>0.3599447419734818</v>
       </c>
       <c r="T62">
-        <v>1.878764159235836</v>
+        <v>1.921270135689136</v>
       </c>
       <c r="U62">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.541383927143451</v>
+        <v>3.331170579789164</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1697041993696579</v>
+        <v>0.1693655439142902</v>
       </c>
       <c r="C63">
-        <v>1.084539255067612</v>
+        <v>1.073538239844572</v>
       </c>
       <c r="D63">
-        <v>2.064799255067612</v>
+        <v>2.070458239844572</v>
       </c>
       <c r="E63">
-        <v>0.28626</v>
+        <v>0.3029199999999999</v>
       </c>
       <c r="F63">
-        <v>1.01626</v>
+        <v>1.03292</v>
       </c>
       <c r="G63">
         <v>0.036</v>
@@ -6435,28 +6435,28 @@
         <v>0.217</v>
       </c>
       <c r="M63">
-        <v>0.065142266</v>
+        <v>0.066210172</v>
       </c>
       <c r="N63">
-        <v>0.151857734</v>
+        <v>0.150789828</v>
       </c>
       <c r="O63">
-        <v>0.03796443349999999</v>
+        <v>0.03769745699999999</v>
       </c>
       <c r="P63">
-        <v>0.1138933005</v>
+        <v>0.113092371</v>
       </c>
       <c r="Q63">
-        <v>0.1668933005</v>
+        <v>0.166092371</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3599447419734818</v>
+        <v>0.367260641879711</v>
       </c>
       <c r="T63">
-        <v>1.921270135689136</v>
+        <v>1.966013268797872</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.331170579789164</v>
+        <v>3.27744202205063</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1693655439142902</v>
+        <v>0.1690268884589225</v>
       </c>
       <c r="C64">
-        <v>1.073538239844572</v>
+        <v>1.062568328970438</v>
       </c>
       <c r="D64">
-        <v>2.070458239844572</v>
+        <v>2.076148328970438</v>
       </c>
       <c r="E64">
-        <v>0.3029199999999999</v>
+        <v>0.31958</v>
       </c>
       <c r="F64">
-        <v>1.03292</v>
+        <v>1.04958</v>
       </c>
       <c r="G64">
         <v>0.036</v>
@@ -6517,28 +6517,28 @@
         <v>0.217</v>
       </c>
       <c r="M64">
-        <v>0.066210172</v>
+        <v>0.06727807800000001</v>
       </c>
       <c r="N64">
-        <v>0.150789828</v>
+        <v>0.149721922</v>
       </c>
       <c r="O64">
-        <v>0.03769745699999999</v>
+        <v>0.03743048049999999</v>
       </c>
       <c r="P64">
-        <v>0.113092371</v>
+        <v>0.1122914415</v>
       </c>
       <c r="Q64">
-        <v>0.166092371</v>
+        <v>0.1652914415</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.367260641879711</v>
+        <v>0.3749719958349255</v>
       </c>
       <c r="T64">
-        <v>1.966013268797872</v>
+        <v>2.013174949642216</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.27744202205063</v>
+        <v>3.22541913281173</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1690268884589225</v>
+        <v>0.1686882330035547</v>
       </c>
       <c r="C65">
-        <v>1.062568328970438</v>
+        <v>1.051629779597351</v>
       </c>
       <c r="D65">
-        <v>2.076148328970438</v>
+        <v>2.081869779597351</v>
       </c>
       <c r="E65">
-        <v>0.31958</v>
+        <v>0.3362400000000001</v>
       </c>
       <c r="F65">
-        <v>1.04958</v>
+        <v>1.06624</v>
       </c>
       <c r="G65">
         <v>0.036</v>
@@ -6599,28 +6599,28 @@
         <v>0.217</v>
       </c>
       <c r="M65">
-        <v>0.06727807800000001</v>
+        <v>0.06834598400000001</v>
       </c>
       <c r="N65">
-        <v>0.149721922</v>
+        <v>0.1486540159999999</v>
       </c>
       <c r="O65">
-        <v>0.03743048049999999</v>
+        <v>0.03716350399999999</v>
       </c>
       <c r="P65">
-        <v>0.1122914415</v>
+        <v>0.111490512</v>
       </c>
       <c r="Q65">
-        <v>0.1652914415</v>
+        <v>0.1644905119999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3749719958349255</v>
+        <v>0.3831117583432075</v>
       </c>
       <c r="T65">
-        <v>2.013174949642216</v>
+        <v>2.062956723866801</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.22541913281173</v>
+        <v>3.175021958861547</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1686882330035547</v>
+        <v>0.168349577548187</v>
       </c>
       <c r="C66">
-        <v>1.051629779597351</v>
+        <v>1.040722851719926</v>
       </c>
       <c r="D66">
-        <v>2.081869779597351</v>
+        <v>2.087622851719926</v>
       </c>
       <c r="E66">
-        <v>0.3362400000000001</v>
+        <v>0.3529</v>
       </c>
       <c r="F66">
-        <v>1.06624</v>
+        <v>1.0829</v>
       </c>
       <c r="G66">
         <v>0.036</v>
@@ -6681,28 +6681,28 @@
         <v>0.217</v>
       </c>
       <c r="M66">
-        <v>0.06834598400000001</v>
+        <v>0.06941389000000001</v>
       </c>
       <c r="N66">
-        <v>0.1486540159999999</v>
+        <v>0.14758611</v>
       </c>
       <c r="O66">
-        <v>0.03716350399999999</v>
+        <v>0.03689652749999999</v>
       </c>
       <c r="P66">
-        <v>0.111490512</v>
+        <v>0.1106895825</v>
       </c>
       <c r="Q66">
-        <v>0.1644905119999999</v>
+        <v>0.1636895825</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3831117583432075</v>
+        <v>0.3917166501376771</v>
       </c>
       <c r="T66">
-        <v>2.062956723866801</v>
+        <v>2.11558317090422</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.175021958861547</v>
+        <v>3.126175467186754</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.168349577548187</v>
+        <v>0.1680109220928193</v>
       </c>
       <c r="C67">
-        <v>1.040722851719926</v>
+        <v>1.029847808214636</v>
       </c>
       <c r="D67">
-        <v>2.087622851719926</v>
+        <v>2.093407808214636</v>
       </c>
       <c r="E67">
-        <v>0.3529</v>
+        <v>0.3695600000000001</v>
       </c>
       <c r="F67">
-        <v>1.0829</v>
+        <v>1.09956</v>
       </c>
       <c r="G67">
         <v>0.036</v>
@@ -6763,28 +6763,28 @@
         <v>0.217</v>
       </c>
       <c r="M67">
-        <v>0.06941389000000001</v>
+        <v>0.07048179600000001</v>
       </c>
       <c r="N67">
-        <v>0.14758611</v>
+        <v>0.146518204</v>
       </c>
       <c r="O67">
-        <v>0.03689652749999999</v>
+        <v>0.03662955099999999</v>
       </c>
       <c r="P67">
-        <v>0.1106895825</v>
+        <v>0.109888653</v>
       </c>
       <c r="Q67">
-        <v>0.1636895825</v>
+        <v>0.162888653</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3917166501376771</v>
+        <v>0.4008277120377037</v>
       </c>
       <c r="T67">
-        <v>2.11558317090422</v>
+        <v>2.17130529129678</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.126175467186754</v>
+        <v>3.078809172229378</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1680109220928193</v>
+        <v>0.1676722666374516</v>
       </c>
       <c r="C68">
-        <v>1.029847808214636</v>
+        <v>1.019004914879848</v>
       </c>
       <c r="D68">
-        <v>2.093407808214636</v>
+        <v>2.099224914879848</v>
       </c>
       <c r="E68">
-        <v>0.3695600000000001</v>
+        <v>0.38622</v>
       </c>
       <c r="F68">
-        <v>1.09956</v>
+        <v>1.11622</v>
       </c>
       <c r="G68">
         <v>0.036</v>
@@ -6845,28 +6845,28 @@
         <v>0.217</v>
       </c>
       <c r="M68">
-        <v>0.07048179600000001</v>
+        <v>0.07154970200000001</v>
       </c>
       <c r="N68">
-        <v>0.146518204</v>
+        <v>0.145450298</v>
       </c>
       <c r="O68">
-        <v>0.03662955099999999</v>
+        <v>0.03636257449999999</v>
       </c>
       <c r="P68">
-        <v>0.109888653</v>
+        <v>0.1090877235</v>
       </c>
       <c r="Q68">
-        <v>0.162888653</v>
+        <v>0.1620877235</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4008277120377037</v>
+        <v>0.4104909595074289</v>
       </c>
       <c r="T68">
-        <v>2.17130529129678</v>
+        <v>2.23040450989495</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.078809172229378</v>
+        <v>3.032856796524463</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1676722666374516</v>
+        <v>0.1713116111820838</v>
       </c>
       <c r="C69">
-        <v>1.019004914879848</v>
+        <v>0.9414756242224227</v>
       </c>
       <c r="D69">
-        <v>2.099224914879848</v>
+        <v>2.038355624222423</v>
       </c>
       <c r="E69">
-        <v>0.38622</v>
+        <v>0.4028800000000001</v>
       </c>
       <c r="F69">
-        <v>1.11622</v>
+        <v>1.13288</v>
       </c>
       <c r="G69">
         <v>0.036</v>
@@ -6927,45 +6927,45 @@
         <v>0.217</v>
       </c>
       <c r="M69">
-        <v>0.07154970200000001</v>
+        <v>0.08145407200000002</v>
       </c>
       <c r="N69">
-        <v>0.145450298</v>
+        <v>0.135545928</v>
       </c>
       <c r="O69">
-        <v>0.03636257449999999</v>
+        <v>0.03388648199999999</v>
       </c>
       <c r="P69">
-        <v>0.1090877235</v>
+        <v>0.101659446</v>
       </c>
       <c r="Q69">
-        <v>0.1620877235</v>
+        <v>0.154659446</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4104909595074289</v>
+        <v>0.4207581599440119</v>
       </c>
       <c r="T69">
-        <v>2.23040450989495</v>
+        <v>2.293197429655506</v>
       </c>
       <c r="U69">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.032856796524463</v>
+        <v>2.664077984953287</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1713116111820838</v>
+        <v>0.1710314557267161</v>
       </c>
       <c r="C70">
-        <v>0.9414756242224227</v>
+        <v>0.9293756322874214</v>
       </c>
       <c r="D70">
-        <v>2.038355624222423</v>
+        <v>2.042915632287421</v>
       </c>
       <c r="E70">
-        <v>0.4028800000000001</v>
+        <v>0.41954</v>
       </c>
       <c r="F70">
-        <v>1.13288</v>
+        <v>1.14954</v>
       </c>
       <c r="G70">
         <v>0.036</v>
@@ -7009,28 +7009,28 @@
         <v>0.217</v>
       </c>
       <c r="M70">
-        <v>0.08145407200000002</v>
+        <v>0.082651926</v>
       </c>
       <c r="N70">
-        <v>0.135545928</v>
+        <v>0.134348074</v>
       </c>
       <c r="O70">
-        <v>0.03388648199999999</v>
+        <v>0.0335870185</v>
       </c>
       <c r="P70">
-        <v>0.101659446</v>
+        <v>0.1007610555</v>
       </c>
       <c r="Q70">
-        <v>0.154659446</v>
+        <v>0.1537610555</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4207581599440119</v>
+        <v>0.4316877604087617</v>
       </c>
       <c r="T70">
-        <v>2.293197429655506</v>
+        <v>2.360041505529647</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.664077984953287</v>
+        <v>2.625468159084399</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1710314557267161</v>
+        <v>0.1707513002713484</v>
       </c>
       <c r="C71">
-        <v>0.9293756322874214</v>
+        <v>0.9172960884971479</v>
       </c>
       <c r="D71">
-        <v>2.042915632287421</v>
+        <v>2.047496088497148</v>
       </c>
       <c r="E71">
-        <v>0.41954</v>
+        <v>0.4362000000000001</v>
       </c>
       <c r="F71">
-        <v>1.14954</v>
+        <v>1.1662</v>
       </c>
       <c r="G71">
         <v>0.036</v>
@@ -7091,28 +7091,28 @@
         <v>0.217</v>
       </c>
       <c r="M71">
-        <v>0.082651926</v>
+        <v>0.08384978000000001</v>
       </c>
       <c r="N71">
-        <v>0.134348074</v>
+        <v>0.13315022</v>
       </c>
       <c r="O71">
-        <v>0.0335870185</v>
+        <v>0.03328755499999999</v>
       </c>
       <c r="P71">
-        <v>0.1007610555</v>
+        <v>0.09986266499999996</v>
       </c>
       <c r="Q71">
-        <v>0.1537610555</v>
+        <v>0.152862665</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4316877604087617</v>
+        <v>0.4433460009044947</v>
       </c>
       <c r="T71">
-        <v>2.360041505529647</v>
+        <v>2.43134185312873</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.625468159084399</v>
+        <v>2.587961471097478</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1707513002713484</v>
+        <v>0.1704711448159807</v>
       </c>
       <c r="C72">
-        <v>0.9172960884971479</v>
+        <v>0.9052371307020881</v>
       </c>
       <c r="D72">
-        <v>2.047496088497148</v>
+        <v>2.052097130702088</v>
       </c>
       <c r="E72">
-        <v>0.4362000000000001</v>
+        <v>0.45286</v>
       </c>
       <c r="F72">
-        <v>1.1662</v>
+        <v>1.18286</v>
       </c>
       <c r="G72">
         <v>0.036</v>
@@ -7173,28 +7173,28 @@
         <v>0.217</v>
       </c>
       <c r="M72">
-        <v>0.08384978000000001</v>
+        <v>0.08504763400000001</v>
       </c>
       <c r="N72">
-        <v>0.13315022</v>
+        <v>0.131952366</v>
       </c>
       <c r="O72">
-        <v>0.03328755499999999</v>
+        <v>0.03298809149999999</v>
       </c>
       <c r="P72">
-        <v>0.09986266499999996</v>
+        <v>0.09896427449999998</v>
       </c>
       <c r="Q72">
-        <v>0.152862665</v>
+        <v>0.1519642745</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4433460009044947</v>
+        <v>0.4558082579861403</v>
       </c>
       <c r="T72">
-        <v>2.43134185312873</v>
+        <v>2.507559466079474</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.587961471097478</v>
+        <v>2.551511309532725</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1704711448159807</v>
+        <v>0.1701909893606129</v>
       </c>
       <c r="C73">
-        <v>0.9052371307020883</v>
+        <v>0.8931988979946051</v>
       </c>
       <c r="D73">
-        <v>2.052097130702088</v>
+        <v>2.056718897994605</v>
       </c>
       <c r="E73">
-        <v>0.4528599999999998</v>
+        <v>0.4695199999999999</v>
       </c>
       <c r="F73">
-        <v>1.18286</v>
+        <v>1.19952</v>
       </c>
       <c r="G73">
         <v>0.036</v>
@@ -7255,28 +7255,28 @@
         <v>0.217</v>
       </c>
       <c r="M73">
-        <v>0.085047634</v>
+        <v>0.086245488</v>
       </c>
       <c r="N73">
-        <v>0.131952366</v>
+        <v>0.130754512</v>
       </c>
       <c r="O73">
-        <v>0.0329880915</v>
+        <v>0.032688628</v>
       </c>
       <c r="P73">
-        <v>0.09896427449999999</v>
+        <v>0.09806588399999999</v>
       </c>
       <c r="Q73">
-        <v>0.1519642745</v>
+        <v>0.151065884</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4558082579861402</v>
+        <v>0.4691606762879033</v>
       </c>
       <c r="T73">
-        <v>2.507559466079473</v>
+        <v>2.589221194240984</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.551511309532726</v>
+        <v>2.516073652455883</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1701909893606129</v>
+        <v>0.1720460839052452</v>
       </c>
       <c r="C74">
-        <v>0.8931988979946051</v>
+        <v>0.8463169070267458</v>
       </c>
       <c r="D74">
-        <v>2.056718897994605</v>
+        <v>2.026496907026746</v>
       </c>
       <c r="E74">
-        <v>0.4695199999999999</v>
+        <v>0.4861799999999998</v>
       </c>
       <c r="F74">
-        <v>1.19952</v>
+        <v>1.21618</v>
       </c>
       <c r="G74">
         <v>0.036</v>
@@ -7337,45 +7337,45 @@
         <v>0.217</v>
       </c>
       <c r="M74">
-        <v>0.086245488</v>
+        <v>0.09218644399999999</v>
       </c>
       <c r="N74">
-        <v>0.130754512</v>
+        <v>0.124813556</v>
       </c>
       <c r="O74">
-        <v>0.032688628</v>
+        <v>0.03120338899999999</v>
       </c>
       <c r="P74">
-        <v>0.09806588399999999</v>
+        <v>0.09361016699999998</v>
       </c>
       <c r="Q74">
-        <v>0.151065884</v>
+        <v>0.146610167</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4691606762879033</v>
+        <v>0.4835021626120193</v>
       </c>
       <c r="T74">
-        <v>2.589221194240984</v>
+        <v>2.676931939303349</v>
       </c>
       <c r="U74">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.516073652455883</v>
+        <v>2.353925269099218</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1720460839052452</v>
+        <v>0.1717951784498775</v>
       </c>
       <c r="C75">
-        <v>0.8463169070267458</v>
+        <v>0.8336924513667312</v>
       </c>
       <c r="D75">
-        <v>2.026496907026746</v>
+        <v>2.030532451366731</v>
       </c>
       <c r="E75">
-        <v>0.4861799999999998</v>
+        <v>0.50284</v>
       </c>
       <c r="F75">
-        <v>1.21618</v>
+        <v>1.23284</v>
       </c>
       <c r="G75">
         <v>0.036</v>
@@ -7419,28 +7419,28 @@
         <v>0.217</v>
       </c>
       <c r="M75">
-        <v>0.09218644399999999</v>
+        <v>0.093449272</v>
       </c>
       <c r="N75">
-        <v>0.124813556</v>
+        <v>0.123550728</v>
       </c>
       <c r="O75">
-        <v>0.03120338899999999</v>
+        <v>0.03088768199999999</v>
       </c>
       <c r="P75">
-        <v>0.09361016699999998</v>
+        <v>0.09266304599999997</v>
       </c>
       <c r="Q75">
-        <v>0.146610167</v>
+        <v>0.145663046</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4835021626120193</v>
+        <v>0.4989468401918364</v>
       </c>
       <c r="T75">
-        <v>2.676931939303349</v>
+        <v>2.771389664755125</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.353925269099218</v>
+        <v>2.322115468165444</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1717951784498775</v>
+        <v>0.1715442729945097</v>
       </c>
       <c r="C76">
-        <v>0.8336924513667312</v>
+        <v>0.821084100457512</v>
       </c>
       <c r="D76">
-        <v>2.030532451366731</v>
+        <v>2.034584100457512</v>
       </c>
       <c r="E76">
-        <v>0.50284</v>
+        <v>0.5194999999999999</v>
       </c>
       <c r="F76">
-        <v>1.23284</v>
+        <v>1.2495</v>
       </c>
       <c r="G76">
         <v>0.036</v>
@@ -7501,28 +7501,28 @@
         <v>0.217</v>
       </c>
       <c r="M76">
-        <v>0.093449272</v>
+        <v>0.09471209999999999</v>
       </c>
       <c r="N76">
-        <v>0.123550728</v>
+        <v>0.1222879</v>
       </c>
       <c r="O76">
-        <v>0.03088768199999999</v>
+        <v>0.03057197499999999</v>
       </c>
       <c r="P76">
-        <v>0.09266304599999997</v>
+        <v>0.09171592499999998</v>
       </c>
       <c r="Q76">
-        <v>0.145663046</v>
+        <v>0.144715925</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4989468401918364</v>
+        <v>0.515627091978039</v>
       </c>
       <c r="T76">
-        <v>2.771389664755125</v>
+        <v>2.873404008243044</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.322115468165444</v>
+        <v>2.291153928589905</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1715442729945097</v>
+        <v>0.171293367539142</v>
       </c>
       <c r="C77">
-        <v>0.821084100457512</v>
+        <v>0.8084919508963015</v>
       </c>
       <c r="D77">
-        <v>2.034584100457512</v>
+        <v>2.038651950896301</v>
       </c>
       <c r="E77">
-        <v>0.5194999999999999</v>
+        <v>0.53616</v>
       </c>
       <c r="F77">
-        <v>1.2495</v>
+        <v>1.26616</v>
       </c>
       <c r="G77">
         <v>0.036</v>
@@ -7583,28 +7583,28 @@
         <v>0.217</v>
       </c>
       <c r="M77">
-        <v>0.09471209999999999</v>
+        <v>0.095974928</v>
       </c>
       <c r="N77">
-        <v>0.1222879</v>
+        <v>0.121025072</v>
       </c>
       <c r="O77">
-        <v>0.03057197499999999</v>
+        <v>0.03025626799999999</v>
       </c>
       <c r="P77">
-        <v>0.09171592499999998</v>
+        <v>0.09076880399999998</v>
       </c>
       <c r="Q77">
-        <v>0.144715925</v>
+        <v>0.143768804</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.515627091978039</v>
+        <v>0.533697364746425</v>
       </c>
       <c r="T77">
-        <v>2.873404008243044</v>
+        <v>2.983919547021622</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.291153928589905</v>
+        <v>2.261007166371617</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.171293367539142</v>
+        <v>0.1710424620837743</v>
       </c>
       <c r="C78">
-        <v>0.8084919508963015</v>
+        <v>0.7959161000543857</v>
       </c>
       <c r="D78">
-        <v>2.038651950896301</v>
+        <v>2.042736100054386</v>
       </c>
       <c r="E78">
-        <v>0.53616</v>
+        <v>0.5528200000000001</v>
       </c>
       <c r="F78">
-        <v>1.26616</v>
+        <v>1.28282</v>
       </c>
       <c r="G78">
         <v>0.036</v>
@@ -7665,28 +7665,28 @@
         <v>0.217</v>
       </c>
       <c r="M78">
-        <v>0.095974928</v>
+        <v>0.09723775600000001</v>
       </c>
       <c r="N78">
-        <v>0.121025072</v>
+        <v>0.119762244</v>
       </c>
       <c r="O78">
-        <v>0.03025626799999999</v>
+        <v>0.02994056099999999</v>
       </c>
       <c r="P78">
-        <v>0.09076880399999998</v>
+        <v>0.08982168299999997</v>
       </c>
       <c r="Q78">
-        <v>0.143768804</v>
+        <v>0.142821683</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.533697364746425</v>
+        <v>0.5533389655816274</v>
       </c>
       <c r="T78">
-        <v>2.983919547021622</v>
+        <v>3.104045132650513</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.261007166371617</v>
+        <v>2.231643436938219</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1710424620837743</v>
+        <v>0.1707915566284066</v>
       </c>
       <c r="C79">
-        <v>0.7959161000543857</v>
+        <v>0.7833566460848993</v>
       </c>
       <c r="D79">
-        <v>2.042736100054386</v>
+        <v>2.046836646084899</v>
       </c>
       <c r="E79">
-        <v>0.5528200000000001</v>
+        <v>0.56948</v>
       </c>
       <c r="F79">
-        <v>1.28282</v>
+        <v>1.29948</v>
       </c>
       <c r="G79">
         <v>0.036</v>
@@ -7747,28 +7747,28 @@
         <v>0.217</v>
       </c>
       <c r="M79">
-        <v>0.09723775600000001</v>
+        <v>0.098500584</v>
       </c>
       <c r="N79">
-        <v>0.119762244</v>
+        <v>0.118499416</v>
       </c>
       <c r="O79">
-        <v>0.02994056099999999</v>
+        <v>0.02962485399999999</v>
       </c>
       <c r="P79">
-        <v>0.08982168299999997</v>
+        <v>0.08887456199999998</v>
       </c>
       <c r="Q79">
-        <v>0.142821683</v>
+        <v>0.141874562</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5533389655816274</v>
+        <v>0.5747661664927572</v>
       </c>
       <c r="T79">
-        <v>3.104045132650513</v>
+        <v>3.235091226063847</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.231643436938219</v>
+        <v>2.20303262364414</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1707915566284066</v>
+        <v>0.1705406511730388</v>
       </c>
       <c r="C80">
-        <v>0.7833566460848993</v>
+        <v>0.7708136879306793</v>
       </c>
       <c r="D80">
-        <v>2.046836646084899</v>
+        <v>2.050953687930679</v>
       </c>
       <c r="E80">
-        <v>0.56948</v>
+        <v>0.5861400000000001</v>
       </c>
       <c r="F80">
-        <v>1.29948</v>
+        <v>1.31614</v>
       </c>
       <c r="G80">
         <v>0.036</v>
@@ -7829,28 +7829,28 @@
         <v>0.217</v>
       </c>
       <c r="M80">
-        <v>0.098500584</v>
+        <v>0.09976341200000001</v>
       </c>
       <c r="N80">
-        <v>0.118499416</v>
+        <v>0.117236588</v>
       </c>
       <c r="O80">
-        <v>0.02962485399999999</v>
+        <v>0.02930914699999999</v>
       </c>
       <c r="P80">
-        <v>0.08887456199999998</v>
+        <v>0.08792744099999997</v>
       </c>
       <c r="Q80">
-        <v>0.141874562</v>
+        <v>0.140927441</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5747661664927572</v>
+        <v>0.598234053204947</v>
       </c>
       <c r="T80">
-        <v>3.235091226063847</v>
+        <v>3.378617899802261</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.20303262364414</v>
+        <v>2.175146134737251</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1705406511730388</v>
+        <v>0.1702897457176711</v>
       </c>
       <c r="C81">
-        <v>0.7708136879306793</v>
+        <v>0.7582873253322318</v>
       </c>
       <c r="D81">
-        <v>2.050953687930679</v>
+        <v>2.055087325332232</v>
       </c>
       <c r="E81">
-        <v>0.5861400000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="F81">
-        <v>1.31614</v>
+        <v>1.3328</v>
       </c>
       <c r="G81">
         <v>0.036</v>
@@ -7911,28 +7911,28 @@
         <v>0.217</v>
       </c>
       <c r="M81">
-        <v>0.09976341200000001</v>
+        <v>0.10102624</v>
       </c>
       <c r="N81">
-        <v>0.117236588</v>
+        <v>0.11597376</v>
       </c>
       <c r="O81">
-        <v>0.02930914699999999</v>
+        <v>0.02899343999999999</v>
       </c>
       <c r="P81">
-        <v>0.08792744099999997</v>
+        <v>0.08698031999999997</v>
       </c>
       <c r="Q81">
-        <v>0.140927441</v>
+        <v>0.13998032</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.598234053204947</v>
+        <v>0.6240487285883558</v>
       </c>
       <c r="T81">
-        <v>3.378617899802261</v>
+        <v>3.536497240914517</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.175146134737251</v>
+        <v>2.147956808053036</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1702897457176711</v>
+        <v>0.1700388402623034</v>
       </c>
       <c r="C82">
-        <v>0.7582873253322318</v>
+        <v>0.7457776588357823</v>
       </c>
       <c r="D82">
-        <v>2.055087325332232</v>
+        <v>2.059237658835782</v>
       </c>
       <c r="E82">
-        <v>0.6028</v>
+        <v>0.6194600000000001</v>
       </c>
       <c r="F82">
-        <v>1.3328</v>
+        <v>1.34946</v>
       </c>
       <c r="G82">
         <v>0.036</v>
@@ -7993,28 +7993,28 @@
         <v>0.217</v>
       </c>
       <c r="M82">
-        <v>0.10102624</v>
+        <v>0.102289068</v>
       </c>
       <c r="N82">
-        <v>0.11597376</v>
+        <v>0.114710932</v>
       </c>
       <c r="O82">
-        <v>0.02899343999999999</v>
+        <v>0.02867773299999999</v>
       </c>
       <c r="P82">
-        <v>0.08698031999999997</v>
+        <v>0.08603319899999998</v>
       </c>
       <c r="Q82">
-        <v>0.13998032</v>
+        <v>0.139033199</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6240487285883558</v>
+        <v>0.6525807382226497</v>
       </c>
       <c r="T82">
-        <v>3.536497240914517</v>
+        <v>3.710995460038588</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.147956808053036</v>
+        <v>2.121438822768431</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1700388402623034</v>
+        <v>0.1697879348069357</v>
       </c>
       <c r="C83">
-        <v>0.7457776588357823</v>
+        <v>0.733284789801429</v>
       </c>
       <c r="D83">
-        <v>2.059237658835782</v>
+        <v>2.063404789801429</v>
       </c>
       <c r="E83">
-        <v>0.6194600000000001</v>
+        <v>0.63612</v>
       </c>
       <c r="F83">
-        <v>1.34946</v>
+        <v>1.36612</v>
       </c>
       <c r="G83">
         <v>0.036</v>
@@ -8075,28 +8075,28 @@
         <v>0.217</v>
       </c>
       <c r="M83">
-        <v>0.102289068</v>
+        <v>0.103551896</v>
       </c>
       <c r="N83">
-        <v>0.114710932</v>
+        <v>0.113448104</v>
       </c>
       <c r="O83">
-        <v>0.02867773299999999</v>
+        <v>0.02836202599999999</v>
       </c>
       <c r="P83">
-        <v>0.08603319899999998</v>
+        <v>0.08508607799999998</v>
       </c>
       <c r="Q83">
-        <v>0.139033199</v>
+        <v>0.138086078</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6525807382226497</v>
+        <v>0.6842829711496429</v>
       </c>
       <c r="T83">
-        <v>3.710995460038588</v>
+        <v>3.904882370176445</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.121438822768431</v>
+        <v>2.095567617612718</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1697879348069357</v>
+        <v>0.169537029351568</v>
       </c>
       <c r="C84">
-        <v>0.733284789801429</v>
+        <v>0.7208088204113932</v>
       </c>
       <c r="D84">
-        <v>2.063404789801429</v>
+        <v>2.067588820411393</v>
       </c>
       <c r="E84">
-        <v>0.63612</v>
+        <v>0.6527800000000001</v>
       </c>
       <c r="F84">
-        <v>1.36612</v>
+        <v>1.38278</v>
       </c>
       <c r="G84">
         <v>0.036</v>
@@ -8157,28 +8157,28 @@
         <v>0.217</v>
       </c>
       <c r="M84">
-        <v>0.103551896</v>
+        <v>0.104814724</v>
       </c>
       <c r="N84">
-        <v>0.113448104</v>
+        <v>0.112185276</v>
       </c>
       <c r="O84">
-        <v>0.02836202599999999</v>
+        <v>0.02804631899999999</v>
       </c>
       <c r="P84">
-        <v>0.08508607799999998</v>
+        <v>0.08413895699999997</v>
       </c>
       <c r="Q84">
-        <v>0.138086078</v>
+        <v>0.137138957</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6842829711496429</v>
+        <v>0.7197148785386355</v>
       </c>
       <c r="T84">
-        <v>3.904882370176445</v>
+        <v>4.121579505036404</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.095567617612718</v>
+        <v>2.070319814990878</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.169537029351568</v>
+        <v>0.1692861238962003</v>
       </c>
       <c r="C85">
-        <v>0.7208088204113932</v>
+        <v>0.708349853678375</v>
       </c>
       <c r="D85">
-        <v>2.067588820411393</v>
+        <v>2.071789853678375</v>
       </c>
       <c r="E85">
-        <v>0.6527800000000001</v>
+        <v>0.66944</v>
       </c>
       <c r="F85">
-        <v>1.38278</v>
+        <v>1.39944</v>
       </c>
       <c r="G85">
         <v>0.036</v>
@@ -8239,28 +8239,28 @@
         <v>0.217</v>
       </c>
       <c r="M85">
-        <v>0.104814724</v>
+        <v>0.106077552</v>
       </c>
       <c r="N85">
-        <v>0.112185276</v>
+        <v>0.110922448</v>
       </c>
       <c r="O85">
-        <v>0.02804631899999999</v>
+        <v>0.02773061199999999</v>
       </c>
       <c r="P85">
-        <v>0.08413895699999997</v>
+        <v>0.08319183599999998</v>
       </c>
       <c r="Q85">
-        <v>0.137138957</v>
+        <v>0.136191836</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7197148785386355</v>
+        <v>0.7595757743512519</v>
       </c>
       <c r="T85">
-        <v>4.121579505036404</v>
+        <v>4.365363781753858</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.070319814990878</v>
+        <v>2.045673150526701</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1692861238962003</v>
+        <v>0.1690352184408326</v>
       </c>
       <c r="C86">
-        <v>0.7083498536783752</v>
+        <v>0.6959079934540024</v>
       </c>
       <c r="D86">
-        <v>2.071789853678375</v>
+        <v>2.076007993454002</v>
       </c>
       <c r="E86">
-        <v>0.6694399999999998</v>
+        <v>0.6860999999999999</v>
       </c>
       <c r="F86">
-        <v>1.39944</v>
+        <v>1.4161</v>
       </c>
       <c r="G86">
         <v>0.036</v>
@@ -8321,28 +8321,28 @@
         <v>0.217</v>
       </c>
       <c r="M86">
-        <v>0.106077552</v>
+        <v>0.10734038</v>
       </c>
       <c r="N86">
-        <v>0.110922448</v>
+        <v>0.10965962</v>
       </c>
       <c r="O86">
-        <v>0.02773061199999999</v>
+        <v>0.02741490499999999</v>
       </c>
       <c r="P86">
-        <v>0.08319183599999999</v>
+        <v>0.08224471499999998</v>
       </c>
       <c r="Q86">
-        <v>0.136191836</v>
+        <v>0.135244715</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7595757743512515</v>
+        <v>0.8047514562722169</v>
       </c>
       <c r="T86">
-        <v>4.365363781753855</v>
+        <v>4.641652628700302</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.045673150526701</v>
+        <v>2.021606407579328</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1690352184408326</v>
+        <v>0.1779433129854648</v>
       </c>
       <c r="C87">
-        <v>0.6959079934540024</v>
+        <v>0.539299364474686</v>
       </c>
       <c r="D87">
-        <v>2.076007993454002</v>
+        <v>1.936059364474686</v>
       </c>
       <c r="E87">
-        <v>0.6860999999999999</v>
+        <v>0.7027599999999998</v>
       </c>
       <c r="F87">
-        <v>1.4161</v>
+        <v>1.43276</v>
       </c>
       <c r="G87">
         <v>0.036</v>
@@ -8403,45 +8403,45 @@
         <v>0.217</v>
       </c>
       <c r="M87">
-        <v>0.10734038</v>
+        <v>0.1289484</v>
       </c>
       <c r="N87">
-        <v>0.10965962</v>
+        <v>0.08805159999999998</v>
       </c>
       <c r="O87">
-        <v>0.02741490499999999</v>
+        <v>0.02201289999999999</v>
       </c>
       <c r="P87">
-        <v>0.08224471499999998</v>
+        <v>0.06603869999999998</v>
       </c>
       <c r="Q87">
-        <v>0.135244715</v>
+        <v>0.1190387</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8047514562722169</v>
+        <v>0.8563808070390342</v>
       </c>
       <c r="T87">
-        <v>4.641652628700302</v>
+        <v>4.957411310924812</v>
       </c>
       <c r="U87">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V87">
         <v>0.25</v>
       </c>
       <c r="W87">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y87">
-        <v>2.021606407579328</v>
+        <v>1.682843680107702</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1779433129854648</v>
+        <v>0.1777989075300971</v>
       </c>
       <c r="C88">
-        <v>0.539299364474686</v>
+        <v>0.5247573936264205</v>
       </c>
       <c r="D88">
-        <v>1.936059364474686</v>
+        <v>1.93817739362642</v>
       </c>
       <c r="E88">
-        <v>0.7027599999999998</v>
+        <v>0.7194199999999999</v>
       </c>
       <c r="F88">
-        <v>1.43276</v>
+        <v>1.44942</v>
       </c>
       <c r="G88">
         <v>0.036</v>
@@ -8485,28 +8485,28 @@
         <v>0.217</v>
       </c>
       <c r="M88">
-        <v>0.1289484</v>
+        <v>0.1304478</v>
       </c>
       <c r="N88">
-        <v>0.08805159999999998</v>
+        <v>0.08655219999999997</v>
       </c>
       <c r="O88">
-        <v>0.02201289999999999</v>
+        <v>0.02163804999999999</v>
       </c>
       <c r="P88">
-        <v>0.06603869999999998</v>
+        <v>0.06491414999999998</v>
       </c>
       <c r="Q88">
-        <v>0.1190387</v>
+        <v>0.11791415</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8563808070390342</v>
+        <v>0.9159531348469006</v>
       </c>
       <c r="T88">
-        <v>4.957411310924812</v>
+        <v>5.321748251953093</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.682843680107702</v>
+        <v>1.663500649301866</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1777989075300971</v>
+        <v>0.1776545020747294</v>
       </c>
       <c r="C89">
-        <v>0.5247573936264205</v>
+        <v>0.5102200620579576</v>
       </c>
       <c r="D89">
-        <v>1.93817739362642</v>
+        <v>1.940300062057958</v>
       </c>
       <c r="E89">
-        <v>0.7194199999999999</v>
+        <v>0.7360800000000001</v>
       </c>
       <c r="F89">
-        <v>1.44942</v>
+        <v>1.46608</v>
       </c>
       <c r="G89">
         <v>0.036</v>
@@ -8567,28 +8567,28 @@
         <v>0.217</v>
       </c>
       <c r="M89">
-        <v>0.1304478</v>
+        <v>0.1319472</v>
       </c>
       <c r="N89">
-        <v>0.08655219999999997</v>
+        <v>0.08505279999999998</v>
       </c>
       <c r="O89">
-        <v>0.02163804999999999</v>
+        <v>0.0212632</v>
       </c>
       <c r="P89">
-        <v>0.06491414999999998</v>
+        <v>0.06378959999999999</v>
       </c>
       <c r="Q89">
-        <v>0.11791415</v>
+        <v>0.1167896</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9159531348469006</v>
+        <v>0.985454183956078</v>
       </c>
       <c r="T89">
-        <v>5.321748251953093</v>
+        <v>5.746808016486088</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.663500649301866</v>
+        <v>1.644597232832527</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1776545020747294</v>
+        <v>0.1775100966193617</v>
       </c>
       <c r="C90">
-        <v>0.5102200620579576</v>
+        <v>0.4956873850286574</v>
       </c>
       <c r="D90">
-        <v>1.940300062057958</v>
+        <v>1.942427385028657</v>
       </c>
       <c r="E90">
-        <v>0.7360800000000001</v>
+        <v>0.75274</v>
       </c>
       <c r="F90">
-        <v>1.46608</v>
+        <v>1.48274</v>
       </c>
       <c r="G90">
         <v>0.036</v>
@@ -8649,28 +8649,28 @@
         <v>0.217</v>
       </c>
       <c r="M90">
-        <v>0.1319472</v>
+        <v>0.1334466</v>
       </c>
       <c r="N90">
-        <v>0.08505279999999998</v>
+        <v>0.08355339999999997</v>
       </c>
       <c r="O90">
-        <v>0.0212632</v>
+        <v>0.02088834999999999</v>
       </c>
       <c r="P90">
-        <v>0.06378959999999999</v>
+        <v>0.06266504999999997</v>
       </c>
       <c r="Q90">
-        <v>0.1167896</v>
+        <v>0.11566505</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.985454183956078</v>
+        <v>1.067591787448742</v>
       </c>
       <c r="T90">
-        <v>5.746808016486088</v>
+        <v>6.249151374570537</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.644597232832527</v>
+        <v>1.626118612238903</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1775100966193617</v>
+        <v>0.1773656911639939</v>
       </c>
       <c r="C91">
-        <v>0.4956873850286574</v>
+        <v>0.4811593778648762</v>
       </c>
       <c r="D91">
-        <v>1.942427385028657</v>
+        <v>1.944559377864876</v>
       </c>
       <c r="E91">
-        <v>0.75274</v>
+        <v>0.7694000000000001</v>
       </c>
       <c r="F91">
-        <v>1.48274</v>
+        <v>1.4994</v>
       </c>
       <c r="G91">
         <v>0.036</v>
@@ -8731,28 +8731,28 @@
         <v>0.217</v>
       </c>
       <c r="M91">
-        <v>0.1334466</v>
+        <v>0.134946</v>
       </c>
       <c r="N91">
-        <v>0.08355339999999997</v>
+        <v>0.08205399999999996</v>
       </c>
       <c r="O91">
-        <v>0.02088834999999999</v>
+        <v>0.02051349999999999</v>
       </c>
       <c r="P91">
-        <v>0.06266504999999997</v>
+        <v>0.06154049999999997</v>
       </c>
       <c r="Q91">
-        <v>0.11566505</v>
+        <v>0.1145405</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.067591787448742</v>
+        <v>1.16615691163994</v>
       </c>
       <c r="T91">
-        <v>6.249151374570537</v>
+        <v>6.851963404271876</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.626118612238903</v>
+        <v>1.608050627658471</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1773656911639939</v>
+        <v>0.1772212857086262</v>
       </c>
       <c r="C92">
-        <v>0.4811593778648762</v>
+        <v>0.4666360559603311</v>
       </c>
       <c r="D92">
-        <v>1.944559377864876</v>
+        <v>1.946696055960331</v>
       </c>
       <c r="E92">
-        <v>0.7694000000000001</v>
+        <v>0.78606</v>
       </c>
       <c r="F92">
-        <v>1.4994</v>
+        <v>1.51606</v>
       </c>
       <c r="G92">
         <v>0.036</v>
@@ -8813,28 +8813,28 @@
         <v>0.217</v>
       </c>
       <c r="M92">
-        <v>0.134946</v>
+        <v>0.1364454</v>
       </c>
       <c r="N92">
-        <v>0.08205399999999996</v>
+        <v>0.08055459999999998</v>
       </c>
       <c r="O92">
-        <v>0.02051349999999999</v>
+        <v>0.02013864999999999</v>
       </c>
       <c r="P92">
-        <v>0.06154049999999997</v>
+        <v>0.06041594999999998</v>
       </c>
       <c r="Q92">
-        <v>0.1145405</v>
+        <v>0.11341595</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.16615691163994</v>
+        <v>1.286625396762514</v>
       </c>
       <c r="T92">
-        <v>6.851963404271876</v>
+        <v>7.588733662795733</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.608050627658471</v>
+        <v>1.590379741640246</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1772212857086262</v>
+        <v>0.1770768802532585</v>
       </c>
       <c r="C93">
-        <v>0.4666360559603311</v>
+        <v>0.4521174347764723</v>
       </c>
       <c r="D93">
-        <v>1.946696055960331</v>
+        <v>1.948837434776472</v>
       </c>
       <c r="E93">
-        <v>0.78606</v>
+        <v>0.8027200000000001</v>
       </c>
       <c r="F93">
-        <v>1.51606</v>
+        <v>1.53272</v>
       </c>
       <c r="G93">
         <v>0.036</v>
@@ -8895,28 +8895,28 @@
         <v>0.217</v>
       </c>
       <c r="M93">
-        <v>0.1364454</v>
+        <v>0.1379448</v>
       </c>
       <c r="N93">
-        <v>0.08055459999999998</v>
+        <v>0.07905519999999996</v>
       </c>
       <c r="O93">
-        <v>0.02013864999999999</v>
+        <v>0.01976379999999999</v>
       </c>
       <c r="P93">
-        <v>0.06041594999999998</v>
+        <v>0.05929139999999997</v>
       </c>
       <c r="Q93">
-        <v>0.11341595</v>
+        <v>0.1122914</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.286625396762514</v>
+        <v>1.437211003165732</v>
       </c>
       <c r="T93">
-        <v>7.588733662795733</v>
+        <v>8.509696485950558</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.590379741640246</v>
+        <v>1.573093005318069</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1770768802532585</v>
+        <v>0.1769324747978908</v>
       </c>
       <c r="C94">
-        <v>0.4521174347764723</v>
+        <v>0.4376035298428571</v>
       </c>
       <c r="D94">
-        <v>1.948837434776472</v>
+        <v>1.950983529842857</v>
       </c>
       <c r="E94">
-        <v>0.8027200000000001</v>
+        <v>0.81938</v>
       </c>
       <c r="F94">
-        <v>1.53272</v>
+        <v>1.54938</v>
       </c>
       <c r="G94">
         <v>0.036</v>
@@ -8977,28 +8977,28 @@
         <v>0.217</v>
       </c>
       <c r="M94">
-        <v>0.1379448</v>
+        <v>0.1394442</v>
       </c>
       <c r="N94">
-        <v>0.07905519999999996</v>
+        <v>0.07755579999999998</v>
       </c>
       <c r="O94">
-        <v>0.01976379999999999</v>
+        <v>0.01938895</v>
       </c>
       <c r="P94">
-        <v>0.05929139999999997</v>
+        <v>0.05816684999999999</v>
       </c>
       <c r="Q94">
-        <v>0.1122914</v>
+        <v>0.11116685</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.437211003165732</v>
+        <v>1.630821068541298</v>
       </c>
       <c r="T94">
-        <v>8.509696485950558</v>
+        <v>9.693791544292473</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.573093005318069</v>
+        <v>1.556178026766262</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1769324747978908</v>
+        <v>0.176788069342523</v>
       </c>
       <c r="C95">
-        <v>0.4376035298428571</v>
+        <v>0.4230943567575225</v>
       </c>
       <c r="D95">
-        <v>1.950983529842857</v>
+        <v>1.953134356757523</v>
       </c>
       <c r="E95">
-        <v>0.81938</v>
+        <v>0.8360400000000001</v>
       </c>
       <c r="F95">
-        <v>1.54938</v>
+        <v>1.56604</v>
       </c>
       <c r="G95">
         <v>0.036</v>
@@ -9059,28 +9059,28 @@
         <v>0.217</v>
       </c>
       <c r="M95">
-        <v>0.1394442</v>
+        <v>0.1409436</v>
       </c>
       <c r="N95">
-        <v>0.07755579999999998</v>
+        <v>0.07605639999999997</v>
       </c>
       <c r="O95">
-        <v>0.01938895</v>
+        <v>0.01901409999999999</v>
       </c>
       <c r="P95">
-        <v>0.05816684999999999</v>
+        <v>0.05704229999999998</v>
       </c>
       <c r="Q95">
-        <v>0.11116685</v>
+        <v>0.1100423</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.630821068541298</v>
+        <v>1.888967822375385</v>
       </c>
       <c r="T95">
-        <v>9.693791544292473</v>
+        <v>11.27258495541503</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.556178026766262</v>
+        <v>1.539622941375131</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.176788069342523</v>
+        <v>0.1766436638871553</v>
       </c>
       <c r="C96">
-        <v>0.4230943567575225</v>
+        <v>0.4085899311873631</v>
       </c>
       <c r="D96">
-        <v>1.953134356757523</v>
+        <v>1.955289931187363</v>
       </c>
       <c r="E96">
-        <v>0.8360400000000001</v>
+        <v>0.8527</v>
       </c>
       <c r="F96">
-        <v>1.56604</v>
+        <v>1.5827</v>
       </c>
       <c r="G96">
         <v>0.036</v>
@@ -9141,28 +9141,28 @@
         <v>0.217</v>
       </c>
       <c r="M96">
-        <v>0.1409436</v>
+        <v>0.142443</v>
       </c>
       <c r="N96">
-        <v>0.07605639999999997</v>
+        <v>0.07455699999999998</v>
       </c>
       <c r="O96">
-        <v>0.01901409999999999</v>
+        <v>0.01863925</v>
       </c>
       <c r="P96">
-        <v>0.05704229999999998</v>
+        <v>0.05591774999999999</v>
       </c>
       <c r="Q96">
-        <v>0.1100423</v>
+        <v>0.10891775</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.888967822375385</v>
+        <v>2.250373277743109</v>
       </c>
       <c r="T96">
-        <v>11.27258495541503</v>
+        <v>13.48289573098661</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.539622941375131</v>
+        <v>1.523416384097499</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1766436638871553</v>
+        <v>0.1764992584317876</v>
       </c>
       <c r="C97">
-        <v>0.4085899311873631</v>
+        <v>0.3940902688685173</v>
       </c>
       <c r="D97">
-        <v>1.955289931187363</v>
+        <v>1.957450268868517</v>
       </c>
       <c r="E97">
-        <v>0.8527</v>
+        <v>0.8693600000000001</v>
       </c>
       <c r="F97">
-        <v>1.5827</v>
+        <v>1.59936</v>
       </c>
       <c r="G97">
         <v>0.036</v>
@@ -9223,28 +9223,28 @@
         <v>0.217</v>
       </c>
       <c r="M97">
-        <v>0.142443</v>
+        <v>0.1439424</v>
       </c>
       <c r="N97">
-        <v>0.07455699999999998</v>
+        <v>0.07305759999999997</v>
       </c>
       <c r="O97">
-        <v>0.01863925</v>
+        <v>0.01826439999999999</v>
       </c>
       <c r="P97">
-        <v>0.05591774999999999</v>
+        <v>0.05479319999999998</v>
       </c>
       <c r="Q97">
-        <v>0.10891775</v>
+        <v>0.1077932</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.250373277743109</v>
+        <v>2.792481460794694</v>
       </c>
       <c r="T97">
-        <v>13.48289573098661</v>
+        <v>16.79836189434398</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.523416384097499</v>
+        <v>1.507547463429816</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1764992584317876</v>
+        <v>0.2237025221844136</v>
       </c>
       <c r="C98">
-        <v>0.3940902688685171</v>
+        <v>-0.1419442750644209</v>
       </c>
       <c r="D98">
-        <v>1.957450268868517</v>
+        <v>1.438075724935579</v>
       </c>
       <c r="E98">
-        <v>0.8693599999999999</v>
+        <v>0.8860199999999998</v>
       </c>
       <c r="F98">
-        <v>1.59936</v>
+        <v>1.61602</v>
       </c>
       <c r="G98">
         <v>0.036</v>
@@ -9305,45 +9305,45 @@
         <v>0.217</v>
       </c>
       <c r="M98">
-        <v>0.1439424</v>
+        <v>0.237231736</v>
       </c>
       <c r="N98">
-        <v>0.07305759999999997</v>
+        <v>-0.02023173600000003</v>
       </c>
       <c r="O98">
-        <v>0.01826439999999999</v>
+        <v>-0.005057934000000007</v>
       </c>
       <c r="P98">
-        <v>0.05479319999999998</v>
+        <v>-0.01517380200000002</v>
       </c>
       <c r="Q98">
-        <v>0.1077932</v>
+        <v>0.03782619799999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.792481460794688</v>
+        <v>3.795651579816582</v>
       </c>
       <c r="T98">
-        <v>16.79836189434394</v>
+        <v>22.93362546292908</v>
       </c>
       <c r="U98">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.25</v>
+        <v>0.2286793534234391</v>
       </c>
       <c r="W98">
-        <v>0.0675</v>
+        <v>0.1132298709174392</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>1.507547463429816</v>
+        <v>0.9147174136937563</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2237025221844136</v>
+        <v>0.2247125221844136</v>
       </c>
       <c r="C99">
-        <v>-0.1419442750644209</v>
+        <v>-0.1667225244996833</v>
       </c>
       <c r="D99">
-        <v>1.438075724935579</v>
+        <v>1.429957475500317</v>
       </c>
       <c r="E99">
-        <v>0.8860199999999998</v>
+        <v>0.9026799999999999</v>
       </c>
       <c r="F99">
-        <v>1.61602</v>
+        <v>1.63268</v>
       </c>
       <c r="G99">
         <v>0.036</v>
@@ -9387,37 +9387,37 @@
         <v>0.217</v>
       </c>
       <c r="M99">
-        <v>0.237231736</v>
+        <v>0.239677424</v>
       </c>
       <c r="N99">
-        <v>-0.02023173600000003</v>
+        <v>-0.02267742400000003</v>
       </c>
       <c r="O99">
-        <v>-0.005057934000000007</v>
+        <v>-0.005669356000000007</v>
       </c>
       <c r="P99">
-        <v>-0.01517380200000002</v>
+        <v>-0.01700806800000002</v>
       </c>
       <c r="Q99">
-        <v>0.03782619799999998</v>
+        <v>0.03599193199999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.795651579816582</v>
+        <v>5.670577369724873</v>
       </c>
       <c r="T99">
-        <v>22.93362546292908</v>
+        <v>34.40043819439362</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2286793534234391</v>
+        <v>0.226345890633404</v>
       </c>
       <c r="W99">
-        <v>0.1132298709174392</v>
+        <v>0.1135724232550163</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9147174136937563</v>
+        <v>0.9053835625336158</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2247125221844136</v>
+        <v>0.2257225221844135</v>
       </c>
       <c r="C100">
-        <v>-0.1667225244996833</v>
+        <v>-0.1914096299043917</v>
       </c>
       <c r="D100">
-        <v>1.429957475500317</v>
+        <v>1.421930370095608</v>
       </c>
       <c r="E100">
-        <v>0.9026799999999999</v>
+        <v>0.9193399999999998</v>
       </c>
       <c r="F100">
-        <v>1.63268</v>
+        <v>1.64934</v>
       </c>
       <c r="G100">
         <v>0.036</v>
@@ -9469,37 +9469,37 @@
         <v>0.217</v>
       </c>
       <c r="M100">
-        <v>0.239677424</v>
+        <v>0.242123112</v>
       </c>
       <c r="N100">
-        <v>-0.02267742400000003</v>
+        <v>-0.02512311200000003</v>
       </c>
       <c r="O100">
-        <v>-0.005669356000000007</v>
+        <v>-0.006280778000000008</v>
       </c>
       <c r="P100">
-        <v>-0.01700806800000002</v>
+        <v>-0.01884233400000002</v>
       </c>
       <c r="Q100">
-        <v>0.03599193199999998</v>
+        <v>0.03415766599999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.670577369724873</v>
+        <v>11.29535473944975</v>
       </c>
       <c r="T100">
-        <v>34.40043819439362</v>
+        <v>68.80087638878723</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.226345890633404</v>
+        <v>0.2240595685057938</v>
       </c>
       <c r="W100">
-        <v>0.1135724232550163</v>
+        <v>0.1139080553433495</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.9053835625336158</v>
+        <v>0.8962382740231754</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2257225221844135</v>
-      </c>
-      <c r="C101">
-        <v>-0.1914096299043917</v>
-      </c>
-      <c r="D101">
-        <v>1.421930370095608</v>
-      </c>
-      <c r="E101">
-        <v>0.9193399999999998</v>
-      </c>
-      <c r="F101">
-        <v>1.64934</v>
-      </c>
-      <c r="G101">
-        <v>0.036</v>
-      </c>
-      <c r="H101">
-        <v>0.9360000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.27</v>
-      </c>
-      <c r="K101">
-        <v>0.053</v>
-      </c>
-      <c r="L101">
-        <v>0.217</v>
-      </c>
-      <c r="M101">
-        <v>0.242123112</v>
-      </c>
-      <c r="N101">
-        <v>-0.02512311200000003</v>
-      </c>
-      <c r="O101">
-        <v>-0.006280778000000008</v>
-      </c>
-      <c r="P101">
-        <v>-0.01884233400000002</v>
-      </c>
-      <c r="Q101">
-        <v>0.03415766599999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.29535473944975</v>
-      </c>
-      <c r="T101">
-        <v>68.80087638878723</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2240595685057938</v>
-      </c>
-      <c r="W101">
-        <v>0.1139080553433495</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8962382740231754</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
